--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이플러스짐 PT 중산점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>aplusgym600@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-977-5755</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym600/222983159417</t>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>493</v>
+        <v>1228</v>
       </c>
       <c r="Q2" t="n">
-        <v>740</v>
+        <v>1082</v>
       </c>
       <c r="R2" t="n">
-        <v>1233</v>
+        <v>2310</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1426431657</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426431657</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
+          <t>resort_13@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>0507-1434-4080</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://blog.naver.com/resort_13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>611</v>
+        <v>558</v>
       </c>
       <c r="Q3" t="n">
-        <v>792</v>
+        <v>895</v>
       </c>
       <c r="R3" t="n">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>1379874016</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/1379874016</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1227</v>
+        <v>1322</v>
       </c>
       <c r="Q4" t="n">
-        <v>1082</v>
+        <v>293</v>
       </c>
       <c r="R4" t="n">
-        <v>2309</v>
+        <v>1615</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,34 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>고포잇짐 헬스&amp;PT 장항점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>go4itgym1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1315-5550</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>https://blog.naver.com/go4itgym1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>558</v>
+        <v>163</v>
       </c>
       <c r="Q5" t="n">
-        <v>896</v>
+        <v>777</v>
       </c>
       <c r="R5" t="n">
-        <v>1454</v>
+        <v>940</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1738952122</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1738952122</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,34 +935,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>gymonelab@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1328-9681</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1320</v>
+        <v>102</v>
       </c>
       <c r="Q6" t="n">
-        <v>289</v>
+        <v>195</v>
       </c>
       <c r="R6" t="n">
-        <v>1609</v>
+        <v>297</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1767374434</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1767374434</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,34 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>고포잇짐 헬스&amp;PT 장항점</t>
+          <t>원잇핏 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>go4itgym1@naver.com</t>
+          <t>oneitfit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1315-5550</t>
+          <t>0507-1400-8861</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/go4itgym1</t>
+          <t>https://blog.naver.com/oneitfit</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="Q7" t="n">
-        <v>784</v>
+        <v>578</v>
       </c>
       <c r="R7" t="n">
-        <v>947</v>
+        <v>805</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1738952122</t>
+          <t>13223584</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738952122</t>
+          <t>https://m.place.naver.com/place/13223584</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+          <t>에이치핏PT&amp;헬스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>dngus8888@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1328-9681</t>
+          <t>0507-1426-3482</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기도 고양시 일산서구 중앙로 1547 3층 307호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+          <t>https://blog.naver.com/dngus8888</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="Q8" t="n">
-        <v>195</v>
+        <v>339</v>
       </c>
       <c r="R8" t="n">
-        <v>297</v>
+        <v>410</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1767374434</t>
+          <t>1639222494</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767374434</t>
+          <t>https://m.place.naver.com/place/1639222494</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,44 +1217,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1445-5805</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>232</v>
+        <v>1176</v>
       </c>
       <c r="Q9" t="n">
-        <v>432</v>
+        <v>874</v>
       </c>
       <c r="R9" t="n">
-        <v>664</v>
+        <v>2050</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,39 +1311,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>디멘션바디랩 필라테스/PT</t>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dimensionbodylab@naver.com</t>
+          <t>momentfit100@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1384-7711</t>
+          <t>0507-1483-9679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 상가 A동 3층 303호</t>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dimensionbodylab</t>
+          <t>http://pf.kakao.com/_xkxdCus</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>579</v>
       </c>
       <c r="Q10" t="n">
-        <v>125</v>
+        <v>838</v>
       </c>
       <c r="R10" t="n">
-        <v>151</v>
+        <v>1417</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1175570585</t>
+          <t>1147827351</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1175570585</t>
+          <t>https://m.place.naver.com/place/1147827351</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>휘트니스칸 헬스&amp;PT&amp;요가&amp;필라테스 주엽점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>kann5555@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1381-8260</t>
+          <t>0507-1396-3191</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,30 +1467,970 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>2037</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>885</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2922</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1797149054</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1797149054</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>더핏퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sky_se@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1411-0772</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sky_se/223038038455</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1110</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1292</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1707178271</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707178271</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>인프라짐 PT 대화역헬스장</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>infragym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1331-5665</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/infragym1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>2377</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4399</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>11579499</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11579499</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>헬로우짐 헬스&amp;PT 백석점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hellogym001@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1383-8244</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hellogym001</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>233</v>
+      </c>
+      <c r="R14" t="n">
+        <v>333</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1528105437</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1528105437</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lifetime1231@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1355-9897</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lifetime1231/223007274910</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1146</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1636</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1618140538</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618140538</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bodyoffgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1381-8260</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyoffgym</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>133</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q16" t="n">
         <v>508</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R16" t="n">
         <v>641</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>32507674</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>핏포유 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fit4u2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1363-6711</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fit4u2019</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>526</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4952</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5478</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>60823193</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/60823193</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>developfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1374-2418</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/developfitness</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>703</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1004</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1707</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1332252606</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332252606</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>베러모션PT스튜디오 장항점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bmotion01@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1451-0635</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1227 동양메이저타워 2층 218호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bmotion01/223868894952</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>194</v>
+      </c>
+      <c r="R19" t="n">
+        <v>231</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1244357356</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1244357356</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>라인업EMS&amp;PT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>line1937@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1385-2208</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1275번길 56 2층 202호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://lineupems.com/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>760</v>
+      </c>
+      <c r="R20" t="n">
+        <v>967</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1500278367</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1500278367</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>탑 메디컬 트레이닝&amp;pt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>woosc9090@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1303-3474</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/woosc9090</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>81</v>
+      </c>
+      <c r="R21" t="n">
+        <v>110</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1747685925</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1747685925</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>1986피트니스 헬스PT 24시 중산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>1986fitness3@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1358-3972</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산동구 중산로 244 6층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>https://blog.naver.com/1986fitness3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1228</v>
+        <v>1304</v>
       </c>
       <c r="Q2" t="n">
-        <v>1082</v>
+        <v>1286</v>
       </c>
       <c r="R2" t="n">
-        <v>2310</v>
+        <v>2590</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,56 +632,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1052772360</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1052772360</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +702,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>558</v>
+        <v>1186</v>
       </c>
       <c r="Q3" t="n">
-        <v>895</v>
+        <v>804</v>
       </c>
       <c r="R3" t="n">
-        <v>1453</v>
+        <v>1990</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +726,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>베러모션PT스튜디오 장항점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>bmotion01@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1451-0635</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산동구 중앙로 1227 동양메이저타워 2층 218호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>https://blog.naver.com/bmotion01/223868894952</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1322</v>
+        <v>38</v>
       </c>
       <c r="Q4" t="n">
-        <v>293</v>
+        <v>236</v>
       </c>
       <c r="R4" t="n">
-        <v>1615</v>
+        <v>274</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +820,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1244357356</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1244357356</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>고포잇짐 헬스&amp;PT 장항점</t>
+          <t>에이치핏PT&amp;헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>go4itgym1@naver.com</t>
+          <t>dngus8888@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1315-5550</t>
+          <t>0507-1426-3482</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+          <t>경기도 고양시 일산서구 중앙로 1547 3층 307호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/go4itgym1</t>
+          <t>https://blog.naver.com/dngus8888</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="Q5" t="n">
-        <v>777</v>
+        <v>337</v>
       </c>
       <c r="R5" t="n">
-        <v>940</v>
+        <v>409</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +914,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1738952122</t>
+          <t>1639222494</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738952122</t>
+          <t>https://m.place.naver.com/place/1639222494</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+          <t>백석PT 뉴레벨 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>newlevelpt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1328-9681</t>
+          <t>0507-1419-5345</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기도 고양시 일산동구 일산로 16 디아뜨크리스탈오피스텔 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+          <t>https://www.instagram.com/newlevelpt/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="Q6" t="n">
-        <v>195</v>
+        <v>366</v>
       </c>
       <c r="R6" t="n">
-        <v>297</v>
+        <v>426</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1008,47 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1767374434</t>
+          <t>628479821</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767374434</t>
+          <t>https://m.place.naver.com/place/628479821</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원잇핏 PT&amp;헬스</t>
+          <t>더블엠여성전용운동센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oneitfit@naver.com</t>
+          <t>ptmickey@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1400-8861</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
+          <t>경기도 고양시 일산서구 경의로 665 한뫼프라자 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oneitfit</t>
+          <t>https://blog.naver.com/ptmickey</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,22 +1074,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>227</v>
+        <v>56</v>
       </c>
       <c r="Q7" t="n">
-        <v>578</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>805</v>
+        <v>63</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1098,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13223584</t>
+          <t>37616187</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13223584</t>
+          <t>https://m.place.naver.com/place/37616187</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에이치핏PT&amp;헬스</t>
+          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dngus8888@naver.com</t>
+          <t>woduddl01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1426-3482</t>
+          <t>0507-1431-9036</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1547 3층 307호</t>
+          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dngus8888</t>
+          <t>https://link.inpock.co.kr/forestgym_2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1170,10 +1162,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yfab</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>71</v>
+        <v>851</v>
       </c>
       <c r="Q8" t="n">
-        <v>339</v>
+        <v>535</v>
       </c>
       <c r="R8" t="n">
-        <v>410</v>
+        <v>1386</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1639222494</t>
+          <t>1320621577</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639222494</t>
+          <t>https://m.place.naver.com/place/1320621577</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>여성전용 오늘도맑음 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>xnlsl@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1460-1801</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기도 고양시 일산동구 장백로 184 605호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://www.instagram.com/pt_malgeum</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1176</v>
+        <v>114</v>
       </c>
       <c r="Q9" t="n">
-        <v>874</v>
+        <v>9</v>
       </c>
       <c r="R9" t="n">
-        <v>2050</v>
+        <v>123</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,56 +1290,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1282698086</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1282698086</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모멘핏 헬스&amp;PT 식사점</t>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>momentfit100@naver.com</t>
+          <t>gymonelab@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1483-9679</t>
+          <t>0507-1328-9681</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxdCus</t>
+          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,22 +1360,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>579</v>
+        <v>101</v>
       </c>
       <c r="Q10" t="n">
-        <v>838</v>
+        <v>196</v>
       </c>
       <c r="R10" t="n">
-        <v>1417</v>
+        <v>297</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1147827351</t>
+          <t>1767374434</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147827351</t>
+          <t>https://m.place.naver.com/place/1767374434</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>휘트니스칸 헬스&amp;PT&amp;요가&amp;필라테스 주엽점</t>
+          <t>백석PT 짐제이와이피 일산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kann5555@naver.com</t>
+          <t>guipok1004@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1396-3191</t>
+          <t>0507-1317-2469</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+          <t>경기도 고양시 일산동구 호수로 340-38 비잔티움1단지 2층 204호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://www.instagram.com/gym_jyp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2037</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="n">
-        <v>885</v>
+        <v>91</v>
       </c>
       <c r="R11" t="n">
-        <v>2922</v>
+        <v>199</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1478,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1797149054</t>
+          <t>1413191309</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797149054</t>
+          <t>https://m.place.naver.com/place/1413191309</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>더핏퍼스널트레이닝</t>
+          <t>제이짐 PT 재활 덕이점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sky_se@naver.com</t>
+          <t>jgymptrehab@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1411-0772</t>
+          <t>0507-1345-7048</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+          <t>경기도 고양시 일산서구 하이파크3로 84 6층 제이짐</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sky_se/223038038455</t>
+          <t>https://blog.naver.com/jgymptrehab/223809138099</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1552,7 +1548,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1561,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="Q12" t="n">
-        <v>1110</v>
+        <v>684</v>
       </c>
       <c r="R12" t="n">
-        <v>1292</v>
+        <v>862</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1707178271</t>
+          <t>1192308600</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707178271</t>
+          <t>https://m.place.naver.com/place/1192308600</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>인프라짐 PT 대화역헬스장</t>
+          <t>라인업EMS&amp;PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>infragym1@naver.com</t>
+          <t>line1937@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1331-5665</t>
+          <t>0507-1385-2208</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 56 2층 202호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/infragym1</t>
+          <t>http://lineupems.com/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1635,7 +1631,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1646,7 +1642,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2377</v>
+        <v>207</v>
       </c>
       <c r="Q13" t="n">
-        <v>2022</v>
+        <v>763</v>
       </c>
       <c r="R13" t="n">
-        <v>4399</v>
+        <v>970</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,51 +1666,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>11579499</t>
+          <t>1500278367</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11579499</t>
+          <t>https://m.place.naver.com/place/1500278367</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>헬로우짐 헬스&amp;PT 백석점</t>
+          <t>씨더블유PT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hellogym001@naver.com</t>
+          <t>tlscnddn2@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1383-8244</t>
+          <t>0507-0178-6183</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
+          <t>경기도 고양시 일산동구 호수로 662 2층 217호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellogym001</t>
+          <t>https://blog.naver.com/tlscnddn2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Q14" t="n">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="R14" t="n">
-        <v>333</v>
+        <v>226</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,51 +1760,51 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1528105437</t>
+          <t>1675929212</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528105437</t>
+          <t>https://m.place.naver.com/place/1675929212</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+          <t>바로그짐 풍동점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lifetime1231@naver.com</t>
+          <t>barofitness@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1355-9897</t>
+          <t>0507-1428-3551</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+          <t>경기도 고양시 일산동구 애니골길 38 바로그짐</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lifetime1231/223007274910</t>
+          <t>https://blog.naver.com/barofitness</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1843,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>490</v>
+        <v>89</v>
       </c>
       <c r="Q15" t="n">
-        <v>1146</v>
+        <v>59</v>
       </c>
       <c r="R15" t="n">
-        <v>1636</v>
+        <v>148</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,51 +1854,51 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1618140538</t>
+          <t>1452871805</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618140538</t>
+          <t>https://m.place.naver.com/place/1452871805</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>테디케이짐 헬스 PT 풍동점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>imka121@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1381-8260</t>
+          <t>0507-1483-6336</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
+          <t>https://blog.naver.com/imka121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1937,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>133</v>
+        <v>536</v>
       </c>
       <c r="Q16" t="n">
-        <v>508</v>
+        <v>255</v>
       </c>
       <c r="R16" t="n">
-        <v>641</v>
+        <v>791</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,51 +1948,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>32507674</t>
+          <t>1011101134</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32507674</t>
+          <t>https://m.place.naver.com/place/1011101134</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>핏포유 탄현점 헬스PT</t>
+          <t>바디에이원짐 헬스/PT/재활</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fit4u2019@naver.com</t>
+          <t>art729@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1363-6711</t>
+          <t>0507-1406-1457</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
+          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fit4u2019</t>
+          <t>https://blog.naver.com/art729/224075467295</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,17 +2023,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="Q17" t="n">
-        <v>4952</v>
+        <v>335</v>
       </c>
       <c r="R17" t="n">
-        <v>5478</v>
+        <v>874</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>60823193</t>
+          <t>1241623010</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60823193</t>
+          <t>https://m.place.naver.com/place/1241623010</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+          <t>재우스짐</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>developfitness@naver.com</t>
+          <t>n52003@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1374-2418</t>
+          <t>0507-1309-1755</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+          <t>경기도 고양시 일산서구 대산로 117</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/developfitness</t>
+          <t>https://www.instagram.com/jaewoos_gym</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2105,7 +2101,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2125,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>703</v>
+        <v>59</v>
       </c>
       <c r="Q18" t="n">
-        <v>1004</v>
+        <v>39</v>
       </c>
       <c r="R18" t="n">
-        <v>1707</v>
+        <v>98</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2140,51 +2136,51 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1332252606</t>
+          <t>1118529364</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332252606</t>
+          <t>https://m.place.naver.com/place/1118529364</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>베러모션PT스튜디오 장항점</t>
+          <t>모티어스 주엽PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bmotion01@naver.com</t>
+          <t>motius_pt@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1451-0635</t>
+          <t>0507-1350-5882</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1227 동양메이저타워 2층 218호</t>
+          <t>경기도 고양시 일산서구 강성로 101 2층 208호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bmotion01/223868894952</t>
+          <t>https://blog.naver.com/motius_pt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2219,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="Q19" t="n">
-        <v>194</v>
+        <v>63</v>
       </c>
       <c r="R19" t="n">
-        <v>231</v>
+        <v>130</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,51 +2230,55 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1244357356</t>
+          <t>1943739312</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1244357356</t>
+          <t>https://m.place.naver.com/place/1943739312</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>라인업EMS&amp;PT</t>
+          <t>팀앤트 파워리프팅</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>line1937@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>59kg_antman@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>boham1025@gmail.com</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1385-2208</t>
+          <t>0507-1339-8089</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 56 2층 202호</t>
+          <t>경기도 고양시 일산동구 일산로286번길 53-22 1층 팀앤트 파워리프팅</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://lineupems.com/</t>
+          <t>https://www.youtube.com/channel/UCFnGeyQ-AjFn3Bn5kkqKgbA</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="Q20" t="n">
-        <v>760</v>
+        <v>56</v>
       </c>
       <c r="R20" t="n">
-        <v>967</v>
+        <v>154</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,51 +2328,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1500278367</t>
+          <t>1109130661</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1500278367</t>
+          <t>https://m.place.naver.com/place/1109130661</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>탑 메디컬 트레이닝&amp;pt</t>
+          <t>디노짐 헬스PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>woosc9090@naver.com</t>
+          <t>dinogym2023@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1303-3474</t>
+          <t>0507-1341-5664</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
+          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woosc9090</t>
+          <t>https://blog.naver.com/dinogym2023</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2407,32 +2407,5358 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>448</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>252</v>
+      </c>
+      <c r="R21" t="n">
+        <v>700</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1693675710</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693675710</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>핏포유 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>fit4u2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1363-6711</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fit4u2019</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>526</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5087</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5613</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>60823193</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/60823193</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>bodyoffgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1381-8260</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyoffgym</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>510</v>
+      </c>
+      <c r="R23" t="n">
+        <v>643</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>32507674</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32507674</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>백석PT 다이어트팩토리짐</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>strom9679@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1371-7277</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 호수로 358-39 동문굿모닝타워1 B1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://일산다이어트팩토리.com/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>325</v>
+      </c>
+      <c r="R24" t="n">
+        <v>507</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>31119951</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31119951</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>베르만짐 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>qpfmaks02@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1349-2708</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjxd4y3</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>669</v>
+      </c>
+      <c r="R25" t="n">
+        <v>993</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1722963960</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1722963960</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>제이앤제이 피트니스 헬스&amp;PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>likegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1314-9695</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강송로 181 일산프라자 2층 제이앤제이 피트니스</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rtjn</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>303</v>
+      </c>
+      <c r="R26" t="n">
+        <v>753</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1181142706</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1181142706</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>백석PT 모티플짐</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mtpg0520@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1447-0538</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1068 리더스프라자 2층 모티플짐</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45ben</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>238</v>
+      </c>
+      <c r="R27" t="n">
+        <v>534</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>37648704</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37648704</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>메피 운동의학 GYM</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mephy_9801@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>031-963-4236</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로11번길 14-26 류정빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>39</v>
+      </c>
+      <c r="R28" t="n">
+        <v>54</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>21127933</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21127933</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>momentfit100@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1483-9679</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xkxdCus</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>581</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>840</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1421</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1147827351</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147827351</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>어나더짐 풍동본점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>anothergym@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 50-38 중앙프라자 A동 2층 203,204호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/anothergym</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>39</v>
+      </c>
+      <c r="R30" t="n">
+        <v>186</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1490064832</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1490064832</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>슈퍼맨짐PT 대화역점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dnflwlqrlacl@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1419-8261</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1565 6층 601호 슈퍼맨짐 대화역점</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcbcbh</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>373</v>
+      </c>
+      <c r="R31" t="n">
+        <v>562</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1457573074</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1457573074</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>원잇핏 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>oneitfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1400-8861</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eey</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>592</v>
+      </c>
+      <c r="R32" t="n">
+        <v>821</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>13223584</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13223584</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>더바디핏PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>seung5105@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1398-9610</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 대산로212번길 24-27 지하1층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yi3h</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>39</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1689017315</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1689017315</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>actgym_02@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1445-5805</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu9oxes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>438</v>
+      </c>
+      <c r="R34" t="n">
+        <v>678</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1033726767</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1033726767</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>탑 메디컬 트레이닝&amp;pt</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>woosc9090@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1303-3474</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk8a</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
         <v>29</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q35" t="n">
+        <v>83</v>
+      </c>
+      <c r="R35" t="n">
+        <v>112</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1747685925</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1747685925</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>헬로우짐 헬스&amp;PT 백석점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hellogym001@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1383-8244</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cr18</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>220</v>
+      </c>
+      <c r="R36" t="n">
+        <v>320</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1528105437</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1528105437</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>제니필라테스 백석점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jenny_3433@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1459-3489</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 장백로 56 크리스탈빌딩 6층 604호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqg39jj</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>343</v>
+      </c>
+      <c r="R37" t="n">
+        <v>491</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>592860746</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/592860746</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kann5555@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1396-3191</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://fitnesskann.com/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41bm5</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>2042</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>876</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2918</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1797149054</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1797149054</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>readybody2@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1359-9680</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461vb</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>671</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1047</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1718</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>776760797</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/776760797</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>엄지네트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ys_0201@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1491-5041</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로93번길 45 B1호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl2cnro</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>61</v>
+      </c>
+      <c r="R40" t="n">
+        <v>73</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1501855812</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1501855812</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>kobygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1374-2418</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we6ins2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>707</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1005</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1712</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1332252606</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332252606</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>투게더휘트니스 일산점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>togetherfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1461-1485</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1346</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>327</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1673</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1161506645</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161506645</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>차차필라테스앤피티 정발산점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>chachapila@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1447-9945</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 34 4층 406호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41ik9</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>367</v>
+      </c>
+      <c r="R43" t="n">
+        <v>514</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1185573190</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185573190</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 마두점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>respect1333@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1335-1380</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lzon</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1374</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1392</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2766</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1420492815</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1420492815</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>여성전용PT 핏바디짐</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>fitbodygym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1331-7858</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 대산로 116 305호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vtrh</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>64</v>
+      </c>
+      <c r="R45" t="n">
+        <v>92</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1315910427</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1315910427</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>헌드레드짐 파주운정점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>hundredgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1327-5413</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>528</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>203</v>
+      </c>
+      <c r="R46" t="n">
+        <v>731</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1101743632</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101743632</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>로얄바디짐</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>wnsvydkdl900@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1357-9683</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1072 9층 902호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>183</v>
+      </c>
+      <c r="R47" t="n">
+        <v>275</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1038850975</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1038850975</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MTO 피트니스 PT 정발산점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jbsfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1467-8389</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f6xw</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>429</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>728</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1157</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1314564243</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1314564243</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 탄현</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goodhabit_th@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1353-2087</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 75 4층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a52b</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>321</v>
+      </c>
+      <c r="R49" t="n">
+        <v>465</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1170704150</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1170704150</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>저스트플레잉</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>justplaying@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>031-965-1106</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://justplaying.co.kr/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>407</v>
+      </c>
+      <c r="R50" t="n">
+        <v>534</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>37452748</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37452748</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>바틀제로핏</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bottlezerofit@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>031-962-0096</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 견달산로 268 2층(씨카우마트2층)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hco7</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>34</v>
+      </c>
+      <c r="R51" t="n">
+        <v>34</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1227017459</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1227017459</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>스포트라이트 트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>spotlight_training@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1423-1387</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 34 4층 401호, 402호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmf991t</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>34</v>
+      </c>
+      <c r="R52" t="n">
+        <v>90</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1161024185</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161024185</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>에이플러스짐휘트니스센터 백마학원가점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>aplusgym500@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl4apt8</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>110</v>
+      </c>
+      <c r="R53" t="n">
+        <v>197</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2067321363</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067321363</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>더핏퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sky_se@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1411-0772</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4izrx</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1123</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1304</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1707178271</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707178271</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1221</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1612</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2833</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1817673935</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817673935</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>온유핏PT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>onu_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1379-8706</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1449 7층 704호 온유핏PT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xx0n</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>170</v>
+      </c>
+      <c r="R56" t="n">
+        <v>233</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1625853344</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1625853344</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>로드짐 야당점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>roadgym86@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1458-6779</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44xex</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
         <v>81</v>
       </c>
-      <c r="R21" t="n">
-        <v>110</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1747685925</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1747685925</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="Q57" t="n">
+        <v>116</v>
+      </c>
+      <c r="R57" t="n">
+        <v>197</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1959563259</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1959563259</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>에이플러스짐 PT 중산점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>aplusgym600@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>031-977-5755</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2t1k29</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>490</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>740</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1230</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1426431657</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1426431657</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>버클다운짐 탄현점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>buckledown1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1358-3972</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1242</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1085</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2327</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1918164834</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1918164834</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>나다워GYM PT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gym_be_myself@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1404-7444</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 산현로17번길 17 . 201호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4kdhr</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>88</v>
+      </c>
+      <c r="R60" t="n">
+        <v>131</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1753187523</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1753187523</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>마두운동장</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>zamzanyaaa@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1412-0138</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1200 802호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42vnp</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>142</v>
+      </c>
+      <c r="R61" t="n">
+        <v>250</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1523650246</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1523650246</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>일산 에이플러스짐 헬스&amp;PT 마두백마학원가점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>aplusgym500@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1449-9334</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 229 B1 에이플러스짐 백마학원가점</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl4apt8</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>489</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>680</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1169</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1400678654</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1400678654</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>플렉스짐 백석점 PT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>flexgym_baekseok@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1361-3798</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>334</v>
+      </c>
+      <c r="R63" t="n">
+        <v>565</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1742139437</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742139437</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>resort_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1434-4080</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zymk</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>561</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>919</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1480</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1379874016</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379874016</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>고포잇짐 헬스&amp;PT 장항점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>go4itgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1315-5550</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4i1nr</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>710</v>
+      </c>
+      <c r="R65" t="n">
+        <v>873</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1738952122</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1738952122</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>lifetime1231@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1355-9897</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lifetime1231/223007274910</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>491</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1140</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1631</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1618140538</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618140538</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>스포애니 마두역점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>spoany64@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1369-7697</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h0gc</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>489</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2211</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2700</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1639489562</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639489562</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>maxoutfitness_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1378-6366</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42bdj</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1269</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>203</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1472</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1674766909</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674766909</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>fitnessel_kintex@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1435-6332</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yi1x</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>315</v>
+      </c>
+      <c r="R69" t="n">
+        <v>523</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1678529668</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1678529668</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>berman_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1483-3436</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvt0jtv</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>685</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1556</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2241</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1924109138</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1924109138</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 백석점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>respect9696@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1431-9696</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/respectgym3</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>289</v>
+      </c>
+      <c r="R71" t="n">
+        <v>498</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1412423288</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412423288</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>인프라짐 PT 대화역헬스장</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>infragym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1331-5665</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9v3</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>2433</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2030</v>
+      </c>
+      <c r="R72" t="n">
+        <v>4463</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>11579499</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11579499</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>라이프바디짐 마두점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>yok134134@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1381-5774</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로196번길 7-5 B1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aqyo</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>165</v>
+      </c>
+      <c r="R73" t="n">
+        <v>295</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1899626531</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1899626531</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>트리플에스짐 후곡PT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>aplus400@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1488-9679</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 576 대성프라자 2층 207,208호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sssgym_official</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>882</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1264</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1107939487</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1107939487</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>올바른PT</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>all_baruenpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1189 굿모닝법조타운 2동 701호 올바른 PT</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5teqy</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>411</v>
+      </c>
+      <c r="R75" t="n">
+        <v>702</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>36763179</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36763179</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>제너럴무브먼트 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>generalmovement@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1363-3703</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1192 802호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b9r6</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>184</v>
+      </c>
+      <c r="R76" t="n">
+        <v>301</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1088736299</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088736299</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45mlf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 중산점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rewind_8990@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1300-9146</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rewind_fitness2</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>167</v>
+        <v>1353</v>
       </c>
       <c r="Q3" t="n">
-        <v>138</v>
+        <v>341</v>
       </c>
       <c r="R3" t="n">
-        <v>305</v>
+        <v>1694</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1726802714</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726802714</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>리와인드 휘트니스 중산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>rewind_8990@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1300-9146</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기 고양시 일산동구 고양대로 762 406~412호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>https://www.instagram.com/rewind_fitness2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u1uf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1353</v>
+        <v>167</v>
       </c>
       <c r="Q4" t="n">
-        <v>337</v>
+        <v>138</v>
       </c>
       <c r="R4" t="n">
-        <v>1690</v>
+        <v>305</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1726802714</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1726802714</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="Q5" t="n">
         <v>1087</v>
       </c>
       <c r="R5" t="n">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기 고양시 일산동구 중앙로 1283 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zymk</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1020,10 @@
         <v>561</v>
       </c>
       <c r="Q6" t="n">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="R6" t="n">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfhd51g</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1145,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orzl</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1217,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>탑 메디컬 트레이닝&amp;pt</t>
+          <t>에이치짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>woosc9090@naver.com</t>
+          <t>ssj783312@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1303-3474</t>
+          <t>031-943-0116</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
+          <t>경기 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woosc9090</t>
+          <t>https://www.instagram.com/hgym24/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1270,7 +1298,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>29</v>
+        <v>367</v>
       </c>
       <c r="Q9" t="n">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="R9" t="n">
-        <v>112</v>
+        <v>787</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1747685925</t>
+          <t>548127191</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747685925</t>
+          <t>https://m.place.naver.com/place/548127191</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>bodyoffgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-943-0116</t>
+          <t>0507-1381-8260</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hgym24/</t>
+          <t>https://blog.naver.com/bodyoffgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>367</v>
+        <v>133</v>
       </c>
       <c r="Q10" t="n">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="R10" t="n">
-        <v>787</v>
+        <v>643</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>548127191</t>
+          <t>32507674</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548127191</t>
+          <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1433,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1381-8260</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,10 +1480,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42s1j</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>133</v>
+        <v>304</v>
       </c>
       <c r="Q11" t="n">
-        <v>510</v>
+        <v>268</v>
       </c>
       <c r="R11" t="n">
-        <v>643</v>
+        <v>572</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32507674</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32507674</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,29 +1536,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>다다짐 헬스&amp;PT 운정본점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>dadagym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>0507-1304-1646</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 파주시 미래로602번길 11 701호,702호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
+          <t>https://blog.naver.com/dadagym/224242550028</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1546,10 +1578,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4v2ogs</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>304</v>
+        <v>59</v>
       </c>
       <c r="Q12" t="n">
-        <v>268</v>
+        <v>70</v>
       </c>
       <c r="R12" t="n">
-        <v>572</v>
+        <v>129</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,15 +1612,113 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>1236035000</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/1236035000</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>리바디피티스튜디오</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rebody7530@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1331-7549</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기 파주시 경의로 1114 505호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjtwmo7</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>28</v>
+      </c>
+      <c r="R13" t="n">
+        <v>63</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2037075259</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037075259</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45mlf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u1uf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="Q5" t="n">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="R5" t="n">
-        <v>2336</v>
+        <v>2340</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zymk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1000,10 @@
         <v>561</v>
       </c>
       <c r="Q6" t="n">
-        <v>929</v>
+        <v>900</v>
       </c>
       <c r="R6" t="n">
-        <v>1490</v>
+        <v>1461</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1071,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfhd51g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1169,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4orzl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1250,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-943-0116</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hgym24/</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1298,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>367</v>
+        <v>1221</v>
       </c>
       <c r="Q9" t="n">
-        <v>420</v>
+        <v>1612</v>
       </c>
       <c r="R9" t="n">
-        <v>787</v>
+        <v>2833</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>548127191</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548127191</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,49 +1311,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1381-8260</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1401,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="Q10" t="n">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="R10" t="n">
-        <v>643</v>
+        <v>683</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>32507674</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32507674</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42s1j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>304</v>
+        <v>679</v>
       </c>
       <c r="Q11" t="n">
-        <v>268</v>
+        <v>1052</v>
       </c>
       <c r="R11" t="n">
-        <v>572</v>
+        <v>1731</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1531,34 +1499,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>다다짐 헬스&amp;PT 운정본점</t>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dadagym@naver.com</t>
+          <t>bodyoffgym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1304-1646</t>
+          <t>0507-1381-8260</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 파주시 미래로602번길 11 701호,702호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dadagym/224242550028</t>
+          <t>https://blog.naver.com/bodyoffgym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1578,14 +1546,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4v2ogs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1597,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="Q12" t="n">
-        <v>70</v>
+        <v>510</v>
       </c>
       <c r="R12" t="n">
-        <v>129</v>
+        <v>643</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1236035000</t>
+          <t>32507674</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236035000</t>
+          <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1629,34 +1593,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>리바디피티스튜디오</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rebody7530@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1331-7549</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1114 505호</t>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1671,19 +1635,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjtwmo7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1695,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>304</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="R13" t="n">
-        <v>63</v>
+        <v>572</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1710,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2037075259</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037075259</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1316,44 +1316,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1445-5805</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>242</v>
+        <v>679</v>
       </c>
       <c r="Q10" t="n">
-        <v>441</v>
+        <v>1053</v>
       </c>
       <c r="R10" t="n">
-        <v>683</v>
+        <v>1732</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>bodyoffgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>0507-1381-8260</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/readybody2</t>
+          <t>https://blog.naver.com/bodyoffgym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>679</v>
+        <v>133</v>
       </c>
       <c r="Q11" t="n">
-        <v>1052</v>
+        <v>510</v>
       </c>
       <c r="R11" t="n">
-        <v>1731</v>
+        <v>643</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,203 +1482,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>32507674</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bodyoffgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1381-8260</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>510</v>
-      </c>
-      <c r="R12" t="n">
-        <v>643</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>32507674</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/32507674</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lounge_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1360-7495</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>304</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>268</v>
-      </c>
-      <c r="R13" t="n">
-        <v>572</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1798562504</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45mlf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -646,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -740,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -774,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rewind_fitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u1uf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -834,41 +846,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1251</v>
+        <v>1221</v>
       </c>
       <c r="Q5" t="n">
-        <v>1089</v>
+        <v>1612</v>
       </c>
       <c r="R5" t="n">
-        <v>2340</v>
+        <v>2833</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>561</v>
+        <v>1251</v>
       </c>
       <c r="Q6" t="n">
-        <v>900</v>
+        <v>1089</v>
       </c>
       <c r="R6" t="n">
-        <v>1461</v>
+        <v>2340</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>resort_13@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1328-9681</t>
+          <t>0507-1434-4080</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zymk</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>101</v>
+        <v>561</v>
       </c>
       <c r="Q7" t="n">
-        <v>196</v>
+        <v>904</v>
       </c>
       <c r="R7" t="n">
-        <v>297</v>
+        <v>1465</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1767374434</t>
+          <t>1379874016</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767374434</t>
+          <t>https://m.place.naver.com/place/1379874016</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1128,39 +1152,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>모멘핏 헬스&amp;PT 식사점</t>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>momentfit100@naver.com</t>
+          <t>gymone10@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1483-9679</t>
+          <t>0507-1328-9681</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxdCus</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1170,28 +1194,32 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfhd51g</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>582</v>
+        <v>101</v>
       </c>
       <c r="Q8" t="n">
-        <v>841</v>
+        <v>196</v>
       </c>
       <c r="R8" t="n">
-        <v>1423</v>
+        <v>297</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1147827351</t>
+          <t>1767374434</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147827351</t>
+          <t>https://m.place.naver.com/place/1767374434</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>momentfit100@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1483-9679</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,23 +1282,27 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orzl</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1221</v>
+        <v>582</v>
       </c>
       <c r="Q9" t="n">
-        <v>1612</v>
+        <v>841</v>
       </c>
       <c r="R9" t="n">
-        <v>2833</v>
+        <v>1423</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1147827351</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1147827351</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>에이치짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>ssj783312@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>031-943-0116</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/readybody2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,7 +1396,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>679</v>
+        <v>367</v>
       </c>
       <c r="Q10" t="n">
-        <v>1053</v>
+        <v>420</v>
       </c>
       <c r="R10" t="n">
-        <v>1732</v>
+        <v>787</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>548127191</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/548127191</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1464,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1442,12 +1474,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1492,7 +1524,203 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lounge_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1360-7495</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42s1j</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>304</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>268</v>
+      </c>
+      <c r="R12" t="n">
+        <v>572</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1798562504</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798562504</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>다다짐 헬스&amp;PT 운정본점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dadagym@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1304-1646</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 파주시 미래로602번길 11 701호,702호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4v2ogs</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>70</v>
+      </c>
+      <c r="R13" t="n">
+        <v>129</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1236035000</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236035000</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 일산점</t>
+          <t>에이플러스짐 PT 중산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rewind9089@naver.com</t>
+          <t>aplusgym600@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1414-2729</t>
+          <t>031-977-5755</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://linktr.ee/junistar3579</t>
+          <t>https://blog.naver.com/aplusgym600/222983159417</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45mlf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>338</v>
+        <v>490</v>
       </c>
       <c r="Q2" t="n">
-        <v>203</v>
+        <v>740</v>
       </c>
       <c r="R2" t="n">
-        <v>541</v>
+        <v>1230</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1294694330</t>
+          <t>1426431657</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294694330</t>
+          <t>https://m.place.naver.com/place/1426431657</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1373-7656</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1353</v>
+        <v>617</v>
       </c>
       <c r="Q3" t="n">
-        <v>341</v>
+        <v>792</v>
       </c>
       <c r="R3" t="n">
-        <v>1694</v>
+        <v>1409</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 중산점</t>
+          <t>리와인드 휘트니스 일산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rewind_8990@naver.com</t>
+          <t>rewind9089@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1300-9146</t>
+          <t>0507-1414-2729</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://linktr.ee/junistar3579</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,27 +784,23 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5u1uf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>167</v>
+        <v>338</v>
       </c>
       <c r="Q4" t="n">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="R4" t="n">
-        <v>305</v>
+        <v>541</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1726802714</t>
+          <t>1294694330</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726802714</t>
+          <t>https://m.place.naver.com/place/1294694330</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,34 +841,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1221</v>
+        <v>1353</v>
       </c>
       <c r="Q5" t="n">
-        <v>1612</v>
+        <v>342</v>
       </c>
       <c r="R5" t="n">
-        <v>2833</v>
+        <v>1695</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -978,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +972,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1000,10 @@
         <v>1251</v>
       </c>
       <c r="Q6" t="n">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="R6" t="n">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/resort_13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,24 +1066,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zymk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1118,10 +1094,10 @@
         <v>561</v>
       </c>
       <c r="Q7" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="R7" t="n">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1157,7 +1133,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymone10@naver.com</t>
+          <t>gymonelab@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1174,7 +1150,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,24 +1160,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfhd51g</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1272,17 +1244,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xkxdCus</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4orzl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1348,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-943-0116</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1396,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>367</v>
+        <v>1221</v>
       </c>
       <c r="Q10" t="n">
-        <v>420</v>
+        <v>1612</v>
       </c>
       <c r="R10" t="n">
-        <v>787</v>
+        <v>2833</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>548127191</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548127191</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,39 +1405,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1381-8260</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1499,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="Q11" t="n">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="R11" t="n">
-        <v>643</v>
+        <v>684</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32507674</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32507674</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1536,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1568,24 +1536,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42s1j</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1597,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>304</v>
+        <v>678</v>
       </c>
       <c r="Q12" t="n">
-        <v>268</v>
+        <v>1055</v>
       </c>
       <c r="R12" t="n">
-        <v>572</v>
+        <v>1733</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,113 +1576,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>다다짐 헬스&amp;PT 운정본점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dadagym@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1304-1646</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 파주시 미래로602번길 11 701호,702호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4v2ogs</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>70</v>
-      </c>
-      <c r="R13" t="n">
-        <v>129</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1236035000</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1236035000</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이플러스짐 PT 중산점</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>aplusgym600@naver.com</t>
+          <t>resort_13@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-977-5755</t>
+          <t>0507-1434-4080</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+          <t>경기 고양시 일산동구 중앙로 1283 10층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym600/222983159417</t>
+          <t>https://blog.naver.com/resort_13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zymk</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>490</v>
+        <v>561</v>
       </c>
       <c r="Q2" t="n">
-        <v>740</v>
+        <v>905</v>
       </c>
       <c r="R2" t="n">
-        <v>1230</v>
+        <v>1466</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1426431657</t>
+          <t>1379874016</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426431657</t>
+          <t>https://m.place.naver.com/place/1379874016</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
+          <t>에이플러스짐 PT 중산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthboy67@naver.com</t>
+          <t>aplusgym600@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1373-7656</t>
+          <t>031-977-5755</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
+          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://linktr.ee/healthboygym67</t>
+          <t>https://blog.naver.com/aplusgym600/222983159417</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2t1k29</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>617</v>
+        <v>489</v>
       </c>
       <c r="Q3" t="n">
-        <v>792</v>
+        <v>740</v>
       </c>
       <c r="R3" t="n">
-        <v>1409</v>
+        <v>1229</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1251452457</t>
+          <t>1426431657</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
+          <t>https://m.place.naver.com/place/1426431657</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 일산점</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rewind9089@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1414-2729</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://linktr.ee/junistar3579</t>
+          <t>https://blog.naver.com/togetherfitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,13 +802,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>338</v>
+        <v>1355</v>
       </c>
       <c r="Q4" t="n">
-        <v>203</v>
+        <v>346</v>
       </c>
       <c r="R4" t="n">
-        <v>541</v>
+        <v>1701</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1294694330</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294694330</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>https://www.instagram.com/buckledowngym.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,15 +895,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1353</v>
+        <v>1252</v>
       </c>
       <c r="Q5" t="n">
-        <v>342</v>
+        <v>1091</v>
       </c>
       <c r="R5" t="n">
-        <v>1695</v>
+        <v>2343</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>gymonelab@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1328-9681</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +993,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfhd51g</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1251</v>
+        <v>101</v>
       </c>
       <c r="Q6" t="n">
-        <v>1090</v>
+        <v>196</v>
       </c>
       <c r="R6" t="n">
-        <v>2341</v>
+        <v>297</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1767374434</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1767374434</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>momentfit100@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1483-9679</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>http://pf.kakao.com/_xkxdCus</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,18 +1091,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4orzl</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="Q7" t="n">
-        <v>905</v>
+        <v>842</v>
       </c>
       <c r="R7" t="n">
-        <v>1466</v>
+        <v>1424</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1147827351</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1147827351</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1328-9681</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기 고���시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+          <t>https://blog.naver.com/5150fitness2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>101</v>
+        <v>1221</v>
       </c>
       <c r="Q8" t="n">
-        <v>196</v>
+        <v>1612</v>
       </c>
       <c r="R8" t="n">
-        <v>297</v>
+        <v>2833</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1767374434</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767374434</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>모멘핏 헬스&amp;PT 식사점</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>momentfit100@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1483-9679</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxdCus</t>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,13 +1292,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu9oxes</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>582</v>
+        <v>244</v>
       </c>
       <c r="Q9" t="n">
-        <v>841</v>
+        <v>441</v>
       </c>
       <c r="R9" t="n">
-        <v>1423</v>
+        <v>685</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1147827351</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147827351</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461vb</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1221</v>
+        <v>679</v>
       </c>
       <c r="Q10" t="n">
-        <v>1612</v>
+        <v>1056</v>
       </c>
       <c r="R10" t="n">
-        <v>2833</v>
+        <v>1735</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,39 +1446,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>에이치짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>ssj783312@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1445-5805</t>
+          <t>031-943-0116</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+          <t>https://www.instagram.com/hgym24/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>243</v>
+        <v>367</v>
       </c>
       <c r="Q11" t="n">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="R11" t="n">
-        <v>684</v>
+        <v>787</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,109 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>548127191</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/548127191</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>레디바디 탄현점 헬스PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>readybody2@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1359-9680</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/readybody2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>678</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1055</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1733</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>776760797</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/776760797</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>디노짐 헬스PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>dinogym2023@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1341-5664</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zymk</t>
+          <t>https://talk.naver.com/ct/w4fu7p</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>561</v>
+        <v>448</v>
       </c>
       <c r="Q2" t="n">
-        <v>905</v>
+        <v>252</v>
       </c>
       <c r="R2" t="n">
-        <v>1466</v>
+        <v>700</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1693675710</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1693675710</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이플러스짐 PT 중산점</t>
+          <t>바로그짐 풍동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>aplusgym600@naver.com</t>
+          <t>barofitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-977-5755</t>
+          <t>0507-1428-3551</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+          <t>경기도 고양시 일산동구 애니골길 38 바로그짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym600/222983159417</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2t1k29</t>
+          <t>https://talk.naver.com/ct/w5uwxf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>489</v>
+        <v>89</v>
       </c>
       <c r="Q3" t="n">
-        <v>740</v>
+        <v>59</v>
       </c>
       <c r="R3" t="n">
-        <v>1229</v>
+        <v>148</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,56 +738,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1426431657</t>
+          <t>1452871805</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426431657</t>
+          <t>https://m.place.naver.com/place/1452871805</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>kann5555@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1396-3191</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/togetherfitness</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
+          <t>https://talk.naver.com/ct/w41bm5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1355</v>
+        <v>2042</v>
       </c>
       <c r="Q4" t="n">
-        <v>346</v>
+        <v>949</v>
       </c>
       <c r="R4" t="n">
-        <v>1701</v>
+        <v>2991</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1797149054</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1797149054</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>로얄바디짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>wnsvydkdl900@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1357-9683</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산동구 중앙로 1072 9층 902호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -900,14 +900,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1252</v>
+        <v>92</v>
       </c>
       <c r="Q5" t="n">
-        <v>1091</v>
+        <v>183</v>
       </c>
       <c r="R5" t="n">
-        <v>2343</v>
+        <v>275</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1038850975</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1038850975</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymonelab@naver.com</t>
+          <t>momentfit100@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1328-9681</t>
+          <t>0507-1483-9679</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymonelab/223934488689?trackingCode=blog_bloghome_searchlist</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,12 +984,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,27 +999,27 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfhd51g</t>
+          <t>https://talk.naver.com/ct/w4orzl</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>101</v>
+        <v>582</v>
       </c>
       <c r="Q6" t="n">
-        <v>196</v>
+        <v>842</v>
       </c>
       <c r="R6" t="n">
-        <v>297</v>
+        <v>1424</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1767374434</t>
+          <t>1147827351</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767374434</t>
+          <t>https://m.place.naver.com/place/1147827351</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1054,39 +1050,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>모멘핏 헬스&amp;PT 식사점</t>
+          <t>탑 메디컬 트레이닝&amp;pt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>momentfit100@naver.com</t>
+          <t>woosc9090@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1483-9679</t>
+          <t>0507-1303-3474</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkxdCus</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1101,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4orzl</t>
+          <t>https://talk.naver.com/ct/w4mk8a</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>582</v>
+        <v>29</v>
       </c>
       <c r="Q7" t="n">
-        <v>842</v>
+        <v>83</v>
       </c>
       <c r="R7" t="n">
-        <v>1424</v>
+        <v>112</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1147827351</t>
+          <t>1747685925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147827351</t>
+          <t>https://m.place.naver.com/place/1747685925</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>플렉스짐 백석점 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>flexgym_baekseok@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1361-3798</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 고���시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/5150fitness2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,24 +1180,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1221</v>
+        <v>231</v>
       </c>
       <c r="Q8" t="n">
-        <v>1612</v>
+        <v>334</v>
       </c>
       <c r="R8" t="n">
-        <v>2833</v>
+        <v>565</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,56 +1220,52 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1742139437</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1742139437</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>올바른PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>all_baruenpt@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1445-5805</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기도 고양시 일산동구 중앙로 1189 굿모닝법조타운 2동 701호 올바른 PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1297,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wu9oxes</t>
+          <t>https://talk.naver.com/ct/w5teqy</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="Q9" t="n">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="R9" t="n">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,51 +1314,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>36763179</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/36763179</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>라인업EMS&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>line1937@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>0507-1385-2208</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 56 2층 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/readybody2</t>
+          <t>http://lineupems.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w461vb</t>
+          <t>https://talk.naver.com/ct/w4ioj1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>679</v>
+        <v>207</v>
       </c>
       <c r="Q10" t="n">
-        <v>1056</v>
+        <v>764</v>
       </c>
       <c r="R10" t="n">
-        <v>1735</v>
+        <v>971</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1412,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>1500278367</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/1500278367</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>로드짐 야당점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>roadgym86@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-943-0116</t>
+          <t>0507-1458-6779</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hgym24/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,7 +1466,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1488,10 +1476,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44xex</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1503,32 +1495,6326 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>116</v>
+      </c>
+      <c r="R11" t="n">
+        <v>197</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1959563259</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1959563259</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 마두점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>respect1333@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1335-1380</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4lzon</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1376</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1393</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2769</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1420492815</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1420492815</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>리스펙짐 PT 백석점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>respect9696@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1431-9696</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7s4785</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>287</v>
+      </c>
+      <c r="R13" t="n">
+        <v>497</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1412423288</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412423288</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>백석PT 뉴레벨 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>newlevelpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1419-5345</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 16 디아뜨크리스탈오피스텔 2층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc5ijn</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>366</v>
+      </c>
+      <c r="R14" t="n">
+        <v>426</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>628479821</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/628479821</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>제니필라테스 백석점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jenny_3433@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1459-3489</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 장백로 56 크리스탈빌딩 6층 604호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqg39jj</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>343</v>
+      </c>
+      <c r="R15" t="n">
+        <v>491</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>592860746</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/592860746</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>내추럴짐</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>whfkfcu@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1370-3813</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 49-36 301호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>18</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1034427772</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1034427772</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>스포애니 마두역점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>spoany64@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1369-7697</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h0gc</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2218</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2706</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1639489562</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639489562</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>프라임핏 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>primefit_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>031-962-2306</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1127</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>289</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1416</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1328418362</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1328418362</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>마두운동장</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>zamzanyaaa@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1412-0138</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1200 802호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/zamzanyaaa</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>142</v>
+      </c>
+      <c r="R19" t="n">
+        <v>250</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1523650246</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1523650246</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>kann666@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1428-1174</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://fitnesskann.com/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4skng</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1187</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>803</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1990</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1533278650</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1533278650</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>테디케이짐 헬스 PT 풍동점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>teddykgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1483-6336</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjaytn7</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>539</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>257</v>
+      </c>
+      <c r="R21" t="n">
+        <v>796</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1011101134</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011101134</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>olof7l6h@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1431-9036</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/forestgym_2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yfab</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>853</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>536</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1389</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1320621577</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320621577</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>하루PT 일산백석점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>haru_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1320-9087</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 백석로86번길 66-14 지하1층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t64e</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>17</v>
+      </c>
+      <c r="R23" t="n">
+        <v>37</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1660604620</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1660604620</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>엄지네트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ys_0201@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1491-5041</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로93번길 45 B1호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl2cnro</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>61</v>
+      </c>
+      <c r="R24" t="n">
+        <v>73</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1501855812</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1501855812</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5150fitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1348-8027</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1222</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1612</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2834</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1817673935</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817673935</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>백석PT 모티플짐</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mtpg0520@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1447-0538</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1068 리더스프라자 2층 모티플짐</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45ben</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>238</v>
+      </c>
+      <c r="R26" t="n">
+        <v>533</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>37648704</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37648704</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>저스트플레잉</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>justplaying@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>031-965-1106</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://justplaying.co.kr/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>408</v>
+      </c>
+      <c r="R27" t="n">
+        <v>535</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>37452748</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37452748</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bodyoffgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1381-8260</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>510</v>
+      </c>
+      <c r="R28" t="n">
+        <v>643</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>32507674</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32507674</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>팀앤트 파워리프팅</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>59kg_antman@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1339-8089</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로286번길 53-22 1층 팀앤트 파워리프팅</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40358</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>56</v>
+      </c>
+      <c r="R29" t="n">
+        <v>154</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1109130661</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109130661</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>백석PT 다이어트팩토리짐</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>strom9679@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1371-7277</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 호수로 358-39 동문굿모닝타워1 B1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>http://일산다이어트팩토리.com/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cxc1</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>325</v>
+      </c>
+      <c r="R30" t="n">
+        <v>507</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>31119951</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31119951</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fitnessel_kintex@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1435-6332</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yi1x</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>315</v>
+      </c>
+      <c r="R31" t="n">
+        <v>520</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1678529668</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1678529668</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>인프라짐 PT 대화역헬스장</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>infragym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1331-5665</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9v3</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>2445</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2033</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4478</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>11579499</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11579499</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>resort_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1434-4080</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zymk</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>561</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>905</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1466</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1379874016</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379874016</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>나다워GYM PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>gym_be_myself@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1404-7444</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 산현로17번길 17 . 201호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4kdhr</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>89</v>
+      </c>
+      <c r="R34" t="n">
+        <v>132</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1753187523</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1753187523</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>백석PT 짐제이와이피 일산점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>guipok1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1317-2469</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 호수로 340-38 비잔티움1단지 2층 204호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym_jyp</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>91</v>
+      </c>
+      <c r="R35" t="n">
+        <v>199</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1413191309</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1413191309</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>버클다운짐 탄현점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>buckledown1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1358-3972</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1252</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1091</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2343</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1918164834</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1918164834</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MTO 피트니스 PT 정발산점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jbsfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1467-8389</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jbsfitness</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>429</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>729</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1158</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1314564243</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1314564243</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>스포트라이트 트레이닝센터</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>spotlight_training@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1423-1387</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 34 4층 401호, 402호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmf991t</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>34</v>
+      </c>
+      <c r="R38" t="n">
+        <v>90</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1161024185</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161024185</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1986피트니스 헬스PT 24시 중산점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1986fitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 244 6층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40uu9</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1306</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2601</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1052772360</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1052772360</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 탄현</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goodhabit_th@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1353-2087</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 75 4층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a52b</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>321</v>
+      </c>
+      <c r="R40" t="n">
+        <v>465</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1170704150</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1170704150</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>헌드레드짐 파주운정점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>hundredgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1327-5413</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>529</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>203</v>
+      </c>
+      <c r="R41" t="n">
+        <v>732</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1101743632</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101743632</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>온유핏PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>onu_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1379-8706</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1449 7층 704호 온유핏PT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xx0n</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>170</v>
+      </c>
+      <c r="R42" t="n">
+        <v>233</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1625853344</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1625853344</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>라이프바디짐 마두점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>yok134134@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1381-5774</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로196번길 7-5 B1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_hxfaYG</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>165</v>
+      </c>
+      <c r="R43" t="n">
+        <v>295</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1899626531</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1899626531</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>제이짐 PT 재활 덕이점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jgymptrehab@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1345-7048</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 하이파크3로 84 6층 제이짐</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49fg3</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>684</v>
+      </c>
+      <c r="R44" t="n">
+        <v>862</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1192308600</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1192308600</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>모티어스 주엽PT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>motius_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1350-5882</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 강성로 101 2층 208호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/motius_pt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>65</v>
+      </c>
+      <c r="R45" t="n">
+        <v>132</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1943739312</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1943739312</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>슈퍼맨짐PT 대화역점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dnflwlqrlacl@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1419-8261</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1565 6층 601호 슈퍼맨짐 대화역점</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcbcbh</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>373</v>
+      </c>
+      <c r="R46" t="n">
+        <v>562</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1457573074</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1457573074</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>베러모션PT스튜디오 장항점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bmotion01@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1451-0635</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1227 동양메이저타워 2층 218호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7gg1x9</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>236</v>
+      </c>
+      <c r="R47" t="n">
+        <v>275</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1244357356</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1244357356</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>바디에이원짐 헬스/PT/재활</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>art729@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1406-1457</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5x0ez</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>543</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>335</v>
+      </c>
+      <c r="R48" t="n">
+        <v>878</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1241623010</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241623010</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>트리플에스짐 후곡PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>aplus400@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1488-9679</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 576 대성프라자 2층 207,208호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wozbktk</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>882</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1264</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1107939487</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1107939487</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>베르만짐 헬스&amp;PT 식사점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>qpfmaks02@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1349-2708</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhhtNn</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>670</v>
+      </c>
+      <c r="R50" t="n">
+        <v>993</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1722963960</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1722963960</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>actgym_02@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1445-5805</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu9oxes</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>442</v>
+      </c>
+      <c r="R51" t="n">
+        <v>686</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1033726767</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1033726767</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>developfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1374-2418</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/developfitness</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>708</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1006</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1714</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1332252606</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332252606</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>일산 에이플러스짐 헬스&amp;PT 마두백마학원가점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>aplusgym500@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1449-9334</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 229 B1 에이플러스짐 백마학원가점</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl4apt8</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>680</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1168</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1400678654</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1400678654</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>재우스짐</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>n52003@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1309-1755</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 대산로 117</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45pjp</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>39</v>
+      </c>
+      <c r="R54" t="n">
+        <v>98</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1118529364</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1118529364</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>투게더휘트니스 일산점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>togetherfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1461-1485</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1356</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>346</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1702</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1161506645</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161506645</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>바틀제로핏</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bottlezerofit@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>031-962-0096</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 견달산로 268 2층(씨카우마트2층)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hco7</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>34</v>
+      </c>
+      <c r="R56" t="n">
+        <v>34</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1227017459</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1227017459</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lifetime1231@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1355-9897</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsf5729</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>491</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1140</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1631</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1618140538</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618140538</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>씨더블유PT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>tlscnddn2@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-0178-6183</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 호수로 662 2층 217호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f6ar</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>122</v>
+      </c>
+      <c r="R58" t="n">
+        <v>226</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1675929212</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1675929212</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>에이플러스짐휘트니스센터 백마학원가점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>aplusgym500@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl4apt8</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>111</v>
+      </c>
+      <c r="R59" t="n">
+        <v>200</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2067321363</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067321363</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>readybody2@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1359-9680</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461vb</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>679</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1056</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1735</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>776760797</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/776760797</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>여성전용PT 핏바디짐</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>fitbodygym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1331-7858</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 대산로 116 305호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vtrh</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>64</v>
+      </c>
+      <c r="R61" t="n">
+        <v>93</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1315910427</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1315910427</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>더블엠여성전용운동센터</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ptmickey@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 경의로 665 한뫼프라자 4층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>7</v>
+      </c>
+      <c r="R62" t="n">
+        <v>63</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>37616187</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37616187</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>maxoutfitness_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1378-6366</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42bdj</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1274</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>203</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1477</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1674766909</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674766909</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>고포잇짐 헬스&amp;PT 장항점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>go4itgym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1315-5550</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/go4itgym1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>712</v>
+      </c>
+      <c r="R64" t="n">
+        <v>876</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1738952122</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1738952122</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>berman_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1483-3436</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvt0jtv</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>689</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1558</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2247</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1924109138</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1924109138</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>메피 운동의학 GYM</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>mephy_9801@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>031-963-4236</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 위시티2로11번길 14-26 류정빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>39</v>
+      </c>
+      <c r="R66" t="n">
+        <v>54</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>21127933</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21127933</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>에이플러스짐 PT 중산점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>aplusgym600@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>031-977-5755</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w2t1k29</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>489</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>740</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1229</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1426431657</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1426431657</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>gymone10@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1328-9681</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfhd51g</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>196</v>
+      </c>
+      <c r="R68" t="n">
+        <v>297</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1767374434</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1767374434</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>에이치핏PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>dngus8888@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1426-3482</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 중앙로 1547 3층 307호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zrcp</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>337</v>
+      </c>
+      <c r="R69" t="n">
+        <v>409</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1639222494</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639222494</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>헬로우짐 헬스&amp;PT 백석점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>hellogym001@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1383-8244</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cr18</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>220</v>
+      </c>
+      <c r="R70" t="n">
+        <v>320</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1528105437</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1528105437</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>더핏퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sky_se@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1411-0772</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4izrx</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1130</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1311</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1707178271</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707178271</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>더바디핏PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>seung5105@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1398-9610</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 대산로212번길 24-27 지하1층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yi3h</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>12</v>
+      </c>
+      <c r="R72" t="n">
+        <v>39</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1689017315</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1689017315</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>차차필라테스앤피티 정발산점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>chachapila@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1447-9945</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 무궁화로 34 4층 406호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41ik9</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q73" t="n">
         <v>367</v>
       </c>
-      <c r="Q11" t="n">
-        <v>420</v>
-      </c>
-      <c r="R11" t="n">
-        <v>787</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>548127191</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/548127191</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="R73" t="n">
+        <v>513</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1185573190</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1185573190</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>어나더짐 풍동본점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>anothergym@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 숲속마을로 50-38 중앙프라자 A동 2층 203,204호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48pv9</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>39</v>
+      </c>
+      <c r="R74" t="n">
+        <v>186</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1490064832</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1490064832</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>원잇핏 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>oneitfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1400-8861</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eey</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>595</v>
+      </c>
+      <c r="R75" t="n">
+        <v>824</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>13223584</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13223584</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>여성전용 오늘도맑음 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>xnlsl@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1460-1801</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 고양시 일산동구 장백로 184 605호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fd01</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>9</v>
+      </c>
+      <c r="R76" t="n">
+        <v>123</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1282698086</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282698086</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -559,29 +559,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>디노짐 헬스PT</t>
+          <t>로얄바디짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dinogym2023@naver.com</t>
+          <t>wnsvydkdl900@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1341-5664</t>
+          <t>0507-1357-9683</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
+          <t>경기도 고양시 일산동구 중앙로 1072 9층 902호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fu7p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>448</v>
+        <v>92</v>
       </c>
       <c r="Q2" t="n">
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="R2" t="n">
-        <v>700</v>
+        <v>275</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1693675710</t>
+          <t>1038850975</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1693675710</t>
+          <t>https://m.place.naver.com/place/1038850975</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,24 +658,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바로그짐 풍동점</t>
+          <t>백석PT 뉴레벨 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>barofitness@naver.com</t>
+          <t>newlevelpt@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1428-3551</t>
+          <t>0507-1419-5345</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 애니골길 38 바로그짐</t>
+          <t>경기도 고양시 일산동구 일산로 16 디아뜨크리스탈오피스텔 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uwxf</t>
+          <t>https://talk.naver.com/ct/wc5ijn</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>366</v>
       </c>
       <c r="R3" t="n">
-        <v>148</v>
+        <v>426</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1452871805</t>
+          <t>628479821</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1452871805</t>
+          <t>https://m.place.naver.com/place/628479821</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,49 +751,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>차차필라테스앤피티 정발산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kann5555@naver.com</t>
+          <t>chachapila@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1396-3191</t>
+          <t>0507-1447-9945</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+          <t>경기도 고양시 일산동구 무궁화로 34 4층 406호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +803,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41bm5</t>
+          <t>https://talk.naver.com/ct/w41ik9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2042</v>
+        <v>146</v>
       </c>
       <c r="Q4" t="n">
-        <v>949</v>
+        <v>367</v>
       </c>
       <c r="R4" t="n">
-        <v>2991</v>
+        <v>513</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1797149054</t>
+          <t>1185573190</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797149054</t>
+          <t>https://m.place.naver.com/place/1185573190</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,24 +854,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>로얄바디짐</t>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wnsvydkdl900@naver.com</t>
+          <t>bodyoffgym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1357-9683</t>
+          <t>0507-1381-8260</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1072 9층 902호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -915,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="Q5" t="n">
-        <v>183</v>
+        <v>510</v>
       </c>
       <c r="R5" t="n">
-        <v>275</v>
+        <v>643</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1038850975</t>
+          <t>32507674</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038850975</t>
+          <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,29 +943,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>모멘핏 헬스&amp;PT 식사점</t>
+          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>momentfit100@naver.com</t>
+          <t>kobygym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1483-9679</t>
+          <t>0507-1374-2418</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
+          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4orzl</t>
+          <t>https://talk.naver.com/ct/we6ins2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>582</v>
+        <v>708</v>
       </c>
       <c r="Q6" t="n">
-        <v>842</v>
+        <v>1006</v>
       </c>
       <c r="R6" t="n">
-        <v>1424</v>
+        <v>1714</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1147827351</t>
+          <t>1332252606</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147827351</t>
+          <t>https://m.place.naver.com/place/1332252606</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,24 +1046,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>탑 메디컬 트레이닝&amp;pt</t>
+          <t>모멘핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>woosc9090@naver.com</t>
+          <t>momentfit100@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1303-3474</t>
+          <t>0507-1483-9679</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
+          <t>경기도 고양시 일산동구 위시티2로 15 골드프라자 3층 모멘핏</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1097,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mk8a</t>
+          <t>https://talk.naver.com/ct/w4orzl</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>29</v>
+        <v>582</v>
       </c>
       <c r="Q7" t="n">
-        <v>83</v>
+        <v>842</v>
       </c>
       <c r="R7" t="n">
-        <v>112</v>
+        <v>1424</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1747685925</t>
+          <t>1147827351</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747685925</t>
+          <t>https://m.place.naver.com/place/1147827351</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,29 +1139,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>플렉스짐 백석점 PT</t>
+          <t>백석PT 모티플짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flexgym_baekseok@naver.com</t>
+          <t>mtpg0520@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1361-3798</t>
+          <t>0507-1447-0538</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
+          <t>경기도 고양시 일산동구 중앙로 1068 리더스프라자 2층 모티플짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,13 +1186,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45ben</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="Q8" t="n">
-        <v>334</v>
+        <v>238</v>
       </c>
       <c r="R8" t="n">
-        <v>565</v>
+        <v>533</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1742139437</t>
+          <t>37648704</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1742139437</t>
+          <t>https://m.place.naver.com/place/37648704</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,45 +1237,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>올바른PT</t>
+          <t>휘트니스칸 주엽점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>all_baruenpt@naver.com</t>
+          <t>kann5555@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1396-3191</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1189 굿모닝법조타운 2동 701호 올바른 PT</t>
+          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,12 +1289,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5teqy</t>
+          <t>https://talk.naver.com/ct/w41bm5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>291</v>
+        <v>2043</v>
       </c>
       <c r="Q9" t="n">
-        <v>411</v>
+        <v>965</v>
       </c>
       <c r="R9" t="n">
-        <v>702</v>
+        <v>3008</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36763179</t>
+          <t>1797149054</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36763179</t>
+          <t>https://m.place.naver.com/place/1797149054</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라인업EMS&amp;PT</t>
+          <t>메피 운동의학 GYM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>line1937@naver.com</t>
+          <t>mephy_9801@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1385-2208</t>
+          <t>031-963-4236</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 56 2층 202호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 14-26 류정빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://lineupems.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1368,7 +1372,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1378,14 +1382,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ioj1</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1393,17 +1393,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>764</v>
+        <v>39</v>
       </c>
       <c r="R10" t="n">
-        <v>971</v>
+        <v>54</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1500278367</t>
+          <t>21127933</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1500278367</t>
+          <t>https://m.place.naver.com/place/21127933</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>로드짐 야당점</t>
+          <t>저스트플레잉</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>roadgym86@naver.com</t>
+          <t>justplaying@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1458-6779</t>
+          <t>031-965-1106</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://justplaying.co.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1476,14 +1476,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44xex</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,17 +1487,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>116</v>
+        <v>408</v>
       </c>
       <c r="R11" t="n">
-        <v>197</v>
+        <v>535</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1506,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1959563259</t>
+          <t>37452748</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1959563259</t>
+          <t>https://m.place.naver.com/place/37452748</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1527,29 +1523,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>리스펙짐 PT 마두점</t>
+          <t>에이플러스짐 PT 중산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>respect1333@naver.com</t>
+          <t>aplusgym600@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1335-1380</t>
+          <t>031-977-5755</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
+          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1579,7 +1575,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4lzon</t>
+          <t>https://talk.naver.com/ct/w2t1k29</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1593,13 +1589,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1376</v>
+        <v>489</v>
       </c>
       <c r="Q12" t="n">
-        <v>1393</v>
+        <v>740</v>
       </c>
       <c r="R12" t="n">
-        <v>2769</v>
+        <v>1229</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,12 +1604,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1420492815</t>
+          <t>1426431657</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420492815</t>
+          <t>https://m.place.naver.com/place/1426431657</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1625,29 +1621,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>리스펙짐 PT 백석점</t>
+          <t>스포트라이트 트레이닝센터</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>respect9696@naver.com</t>
+          <t>spotlight_training@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1431-9696</t>
+          <t>0507-1423-1387</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
+          <t>경기도 고양시 일산동구 무궁화로 34 4층 401호, 402호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1677,7 +1673,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7s4785</t>
+          <t>https://talk.naver.com/ct/wmf991t</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1691,13 +1687,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="Q13" t="n">
-        <v>287</v>
+        <v>34</v>
       </c>
       <c r="R13" t="n">
-        <v>497</v>
+        <v>90</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1706,12 +1702,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1412423288</t>
+          <t>1161024185</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1412423288</t>
+          <t>https://m.place.naver.com/place/1161024185</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1723,29 +1719,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>백석PT 뉴레벨 퍼스널트레이닝</t>
+          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>newlevelpt@naver.com</t>
+          <t>fitnessel_kintex@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1419-5345</t>
+          <t>0507-1435-6332</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 16 디아뜨크리스탈오피스텔 2층</t>
+          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1775,7 +1771,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc5ijn</t>
+          <t>https://talk.naver.com/ct/w5yi1x</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1789,13 +1785,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="Q14" t="n">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="R14" t="n">
-        <v>426</v>
+        <v>520</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1804,12 +1800,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>628479821</t>
+          <t>1678529668</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/628479821</t>
+          <t>https://m.place.naver.com/place/1678529668</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1821,34 +1817,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>제니필라테스 백석점</t>
+          <t>라인업EMS&amp;PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jenny_3433@naver.com</t>
+          <t>line1937@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1459-3489</t>
+          <t>0507-1385-2208</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 장백로 56 크리스탈빌딩 6층 604호</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 56 2층 202호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://lineupems.com/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1858,7 +1854,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1873,7 +1869,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqg39jj</t>
+          <t>https://talk.naver.com/ct/w4ioj1</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1887,13 +1883,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>148</v>
+        <v>207</v>
       </c>
       <c r="Q15" t="n">
-        <v>343</v>
+        <v>764</v>
       </c>
       <c r="R15" t="n">
-        <v>491</v>
+        <v>971</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1902,12 +1898,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>592860746</t>
+          <t>1500278367</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/592860746</t>
+          <t>https://m.place.naver.com/place/1500278367</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1924,24 +1920,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>내추럴짐</t>
+          <t>백석PT 짐제이와이피 일산점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>whfkfcu@naver.com</t>
+          <t>guipok1004@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1370-3813</t>
+          <t>0507-1317-2469</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 49-36 301호</t>
+          <t>경기도 고양시 일산동구 호수로 340-38 비잔티움1단지 2층 204호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1966,10 +1962,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aejq</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>X</t>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="R16" t="n">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1034427772</t>
+          <t>1413191309</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034427772</t>
+          <t>https://m.place.naver.com/place/1413191309</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2018,24 +2018,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>스포애니 마두역점</t>
+          <t>인프라짐 PT 대화역헬스장</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>spoany64@naver.com</t>
+          <t>infragym1@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1369-7697</t>
+          <t>0507-1331-5665</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
+          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h0gc</t>
+          <t>https://talk.naver.com/ct/w5u9v3</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>488</v>
+        <v>2460</v>
       </c>
       <c r="Q17" t="n">
-        <v>2218</v>
+        <v>2033</v>
       </c>
       <c r="R17" t="n">
-        <v>2706</v>
+        <v>4493</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1639489562</t>
+          <t>11579499</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639489562</t>
+          <t>https://m.place.naver.com/place/11579499</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2116,24 +2116,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>프라임핏 헬스&amp;PT 식사점</t>
+          <t>베르만짐 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>primefit_fitness@naver.com</t>
+          <t>qpfmaks02@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>031-962-2306</t>
+          <t>0507-1349-2708</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
+          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2158,13 +2158,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjxd4y3</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2173,13 +2177,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1127</v>
+        <v>323</v>
       </c>
       <c r="Q18" t="n">
-        <v>289</v>
+        <v>669</v>
       </c>
       <c r="R18" t="n">
-        <v>1416</v>
+        <v>992</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2188,12 +2192,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1328418362</t>
+          <t>1722963960</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328418362</t>
+          <t>https://m.place.naver.com/place/1722963960</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2210,29 +2214,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>마두운동장</t>
+          <t>팀앤트 파워리프팅</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>zamzanyaaa@naver.com</t>
+          <t>59kg_antman@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1412-0138</t>
+          <t>0507-1339-8089</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1200 802호</t>
+          <t>경기도 고양시 일산동구 일산로286번길 53-22 1층 팀앤트 파워리프팅</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zamzanyaaa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2242,20 +2246,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40358</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2263,17 +2271,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="Q19" t="n">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="R19" t="n">
-        <v>250</v>
+        <v>154</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2282,12 +2290,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1523650246</t>
+          <t>1109130661</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1523650246</t>
+          <t>https://m.place.naver.com/place/1109130661</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2304,44 +2312,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>MTO 피트니스 PT 정발산점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>jbsfitness@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1467-8389</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기도 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2351,12 +2359,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4skng</t>
+          <t>https://talk.naver.com/ct/w4f6xw</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2365,13 +2373,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1187</v>
+        <v>429</v>
       </c>
       <c r="Q20" t="n">
-        <v>803</v>
+        <v>729</v>
       </c>
       <c r="R20" t="n">
-        <v>1990</v>
+        <v>1158</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2380,12 +2388,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1314564243</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1314564243</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2397,29 +2405,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>테디케이짐 헬스 PT 풍동점</t>
+          <t>라이프바디짐 마두점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>teddykgym@naver.com</t>
+          <t>yok134134@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1483-6336</t>
+          <t>0507-1381-5774</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
+          <t>경기도 고양시 일산동구 정발산로196번길 7-5 B1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2449,12 +2457,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wjaytn7</t>
+          <t>https://talk.naver.com/ct/w4aqyo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2463,13 +2471,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="Q21" t="n">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="R21" t="n">
-        <v>796</v>
+        <v>295</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2478,12 +2486,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1011101134</t>
+          <t>1899626531</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011101134</t>
+          <t>https://m.place.naver.com/place/1899626531</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2495,49 +2503,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
+          <t>하루PT 일산백석점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>olof7l6h@naver.com</t>
+          <t>haru_pt@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1431-9036</t>
+          <t>0507-1320-9087</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
+          <t>경기도 고양시 일산동구 백석로86번길 66-14 지하1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/forestgym_2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2547,7 +2555,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yfab</t>
+          <t>https://talk.naver.com/ct/w5t64e</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2561,13 +2569,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>853</v>
+        <v>20</v>
       </c>
       <c r="Q22" t="n">
-        <v>536</v>
+        <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>1389</v>
+        <v>37</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2576,12 +2584,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1320621577</t>
+          <t>1660604620</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320621577</t>
+          <t>https://m.place.naver.com/place/1660604620</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2598,24 +2606,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>하루PT 일산백석점</t>
+          <t>더바디핏PT&amp;헬스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>haru_pt@naver.com</t>
+          <t>seung5105@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1320-9087</t>
+          <t>0507-1398-9610</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백석로86번길 66-14 지하1층</t>
+          <t>경기도 고양시 일산서구 대산로212번길 24-27 지하1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2645,7 +2653,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t64e</t>
+          <t>https://talk.naver.com/ct/w5yi3h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2659,13 +2667,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2674,12 +2682,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1660604620</t>
+          <t>1689017315</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1660604620</t>
+          <t>https://m.place.naver.com/place/1689017315</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2696,24 +2704,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>엄지네트레이닝PT</t>
+          <t>에이치핏PT&amp;헬스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ys_0201@naver.com</t>
+          <t>dngus8888@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1491-5041</t>
+          <t>0507-1426-3482</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로93번길 45 B1호</t>
+          <t>경기도 고양시 일산서구 중앙로 1547 3층 307호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2743,7 +2751,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl2cnro</t>
+          <t>https://talk.naver.com/ct/w5zrcp</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2757,13 +2765,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>336</v>
       </c>
       <c r="R24" t="n">
-        <v>73</v>
+        <v>408</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2772,12 +2780,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1501855812</t>
+          <t>1639222494</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501855812</t>
+          <t>https://m.place.naver.com/place/1639222494</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2789,29 +2797,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5150피트니스 일산 대화점</t>
+          <t>PT샵 웅동장</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5150fitness2@naver.com</t>
+          <t>zw4175@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1348-8027</t>
+          <t>0507-1334-4398</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
+          <t>경기도 고양시 일산서구 일산로 731 3층 301호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2841,7 +2849,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vwhp</t>
+          <t>https://talk.naver.com/ct/w5zv7h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2855,13 +2863,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1222</v>
+        <v>52</v>
       </c>
       <c r="Q25" t="n">
-        <v>1612</v>
+        <v>29</v>
       </c>
       <c r="R25" t="n">
-        <v>2834</v>
+        <v>81</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2870,12 +2878,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1817673935</t>
+          <t>1971533185</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
+          <t>https://m.place.naver.com/place/1971533185</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2887,29 +2895,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>백석PT 모티플짐</t>
+          <t>스포애니 마두역점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mtpg0520@naver.com</t>
+          <t>spoany64@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1447-0538</t>
+          <t>0507-1369-7697</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1068 리더스프라자 2층 모티플짐</t>
+          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2939,12 +2947,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45ben</t>
+          <t>https://talk.naver.com/ct/w4h0gc</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2953,13 +2961,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>295</v>
+        <v>488</v>
       </c>
       <c r="Q26" t="n">
-        <v>238</v>
+        <v>2220</v>
       </c>
       <c r="R26" t="n">
-        <v>533</v>
+        <v>2708</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2968,12 +2976,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>37648704</t>
+          <t>1639489562</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37648704</t>
+          <t>https://m.place.naver.com/place/1639489562</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2990,29 +2998,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>저스트플레잉</t>
+          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>justplaying@naver.com</t>
+          <t>lifetime1231@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>031-965-1106</t>
+          <t>0507-1355-9897</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 6-13 태경프라자 2층</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://justplaying.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3022,7 +3030,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3032,10 +3040,14 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsf5729</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>X</t>
@@ -3043,17 +3055,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>127</v>
+        <v>491</v>
       </c>
       <c r="Q27" t="n">
-        <v>408</v>
+        <v>1140</v>
       </c>
       <c r="R27" t="n">
-        <v>535</v>
+        <v>1631</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3062,12 +3074,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37452748</t>
+          <t>1618140538</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37452748</t>
+          <t>https://m.place.naver.com/place/1618140538</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3084,24 +3096,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>올바른PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>all_baruenpt@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1381-8260</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기도 고양시 일산동구 중앙로 1189 굿모닝법조타운 2동 701호 올바른 PT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3126,10 +3134,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5teqy</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3141,13 +3153,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>133</v>
+        <v>291</v>
       </c>
       <c r="Q28" t="n">
-        <v>510</v>
+        <v>411</v>
       </c>
       <c r="R28" t="n">
-        <v>643</v>
+        <v>702</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3156,12 +3168,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>32507674</t>
+          <t>36763179</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32507674</t>
+          <t>https://m.place.naver.com/place/36763179</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3178,24 +3190,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>팀앤트 파워리프팅</t>
+          <t>헌드레드짐 파주운정점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>59kg_antman@naver.com</t>
+          <t>hundredgym@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1339-8089</t>
+          <t>0507-1327-5413</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로286번길 53-22 1층 팀앤트 파워리프팅</t>
+          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3220,14 +3232,10 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40358</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>X</t>
@@ -3235,17 +3243,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>98</v>
+        <v>530</v>
       </c>
       <c r="Q29" t="n">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="R29" t="n">
-        <v>154</v>
+        <v>733</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3254,12 +3262,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1109130661</t>
+          <t>1101743632</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109130661</t>
+          <t>https://m.place.naver.com/place/1101743632</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3276,34 +3284,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>백석PT 다이어트팩토리짐</t>
+          <t>나다워GYM PT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>strom9679@naver.com</t>
+          <t>gym_be_myself@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1371-7277</t>
+          <t>0507-1404-7444</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로 358-39 동문굿모닝타워1 B1</t>
+          <t>경기도 고양시 일산서구 산현로17번길 17 . 201호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://일산다이어트팩토리.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3313,7 +3321,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3323,27 +3331,27 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cxc1</t>
+          <t>https://talk.naver.com/ct/w4kdhr</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>182</v>
+        <v>43</v>
       </c>
       <c r="Q30" t="n">
-        <v>325</v>
+        <v>89</v>
       </c>
       <c r="R30" t="n">
-        <v>507</v>
+        <v>132</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3352,12 +3360,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>31119951</t>
+          <t>1753187523</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31119951</t>
+          <t>https://m.place.naver.com/place/1753187523</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3369,29 +3377,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>여성전용 휘트니스엘 플라잉요가 헬스 PT 일산주엽역점</t>
+          <t>일산 에이플러스짐 헬스&amp;PT 마두백마학원가점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fitnessel_kintex@naver.com</t>
+          <t>aplusgym500@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1435-6332</t>
+          <t>0507-1449-9334</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 80 D동 3층 303호</t>
+          <t>경기도 고양시 일산동구 일산로 229 B1 에이플러스짐 백마학원가점</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3421,12 +3429,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yi1x</t>
+          <t>https://talk.naver.com/ct/wl4apt8</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3435,13 +3443,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>205</v>
+        <v>488</v>
       </c>
       <c r="Q31" t="n">
-        <v>315</v>
+        <v>680</v>
       </c>
       <c r="R31" t="n">
-        <v>520</v>
+        <v>1168</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3450,12 +3458,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1678529668</t>
+          <t>1400678654</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678529668</t>
+          <t>https://m.place.naver.com/place/1400678654</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3467,29 +3475,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>인프라짐 PT 대화역헬스장</t>
+          <t>재우스짐</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>infragym1@naver.com</t>
+          <t>n52003@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1331-5665</t>
+          <t>0507-1309-1755</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기도 고양시 일산서구 대산로 117</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3519,12 +3527,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u9v3</t>
+          <t>https://talk.naver.com/ct/w45pjp</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3533,13 +3541,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2445</v>
+        <v>59</v>
       </c>
       <c r="Q32" t="n">
-        <v>2033</v>
+        <v>39</v>
       </c>
       <c r="R32" t="n">
-        <v>4478</v>
+        <v>98</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3548,12 +3556,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>11579499</t>
+          <t>1118529364</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11579499</t>
+          <t>https://m.place.naver.com/place/1118529364</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3570,24 +3578,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>엄지네트레이닝PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>ys_0201@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1491-5041</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기도 고양시 일산동구 무궁화로93번길 45 B1호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3617,7 +3625,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zymk</t>
+          <t>https://talk.naver.com/ct/wl2cnro</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3631,13 +3639,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>561</v>
+        <v>12</v>
       </c>
       <c r="Q33" t="n">
-        <v>905</v>
+        <v>61</v>
       </c>
       <c r="R33" t="n">
-        <v>1466</v>
+        <v>73</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3646,12 +3654,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>1501855812</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/1501855812</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3668,24 +3676,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>나다워GYM PT</t>
+          <t>마두운동장</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>gym_be_myself@naver.com</t>
+          <t>zamzanyaaa@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1404-7444</t>
+          <t>0507-1412-0138</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 산현로17번길 17 . 201호</t>
+          <t>경기도 고양시 일산동구 중앙로 1200 802호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3715,7 +3723,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4kdhr</t>
+          <t>https://talk.naver.com/ct/w42vnp</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3725,17 +3733,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="Q34" t="n">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="R34" t="n">
-        <v>132</v>
+        <v>250</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3744,12 +3752,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1753187523</t>
+          <t>1523650246</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1753187523</t>
+          <t>https://m.place.naver.com/place/1523650246</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3761,34 +3769,34 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>백석PT 짐제이와이피 일산점</t>
+          <t>플렉스짐 백석점 PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>guipok1004@naver.com</t>
+          <t>flexgym_baekseok@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1317-2469</t>
+          <t>0507-1361-3798</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로 340-38 비잔티움1단지 2층 204호</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자3 10층 플렉스짐</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_jyp</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3798,7 +3806,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3823,13 +3831,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="Q35" t="n">
-        <v>91</v>
+        <v>334</v>
       </c>
       <c r="R35" t="n">
-        <v>199</v>
+        <v>565</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3838,12 +3846,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1413191309</t>
+          <t>1742139437</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1413191309</t>
+          <t>https://m.place.naver.com/place/1742139437</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3860,24 +3868,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>버클다운짐 탄현점</t>
+          <t>베러모션PT스튜디오 장항점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>buckledown1234@naver.com</t>
+          <t>bmotion01@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1358-3972</t>
+          <t>0507-1451-0635</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
+          <t>경기도 고양시 일산동구 중앙로 1227 동양메이저타워 2층 218호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3907,7 +3915,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tj13</t>
+          <t>https://talk.naver.com/ct/w7gg1x9</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3921,13 +3929,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1252</v>
+        <v>39</v>
       </c>
       <c r="Q36" t="n">
-        <v>1091</v>
+        <v>236</v>
       </c>
       <c r="R36" t="n">
-        <v>2343</v>
+        <v>275</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3936,12 +3944,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1918164834</t>
+          <t>1244357356</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
+          <t>https://m.place.naver.com/place/1244357356</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3958,29 +3966,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MTO 피트니스 PT 정발산점</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jbsfitness@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1467-8389</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 39 5층 MTO 피트니스 PT 정발산점</t>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jbsfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3990,20 +3998,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461vb</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -4015,13 +4027,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>429</v>
+        <v>679</v>
       </c>
       <c r="Q37" t="n">
-        <v>729</v>
+        <v>1058</v>
       </c>
       <c r="R37" t="n">
-        <v>1158</v>
+        <v>1737</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -4030,12 +4042,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1314564243</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1314564243</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4052,34 +4064,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>스포트라이트 트레이닝센터</t>
+          <t>백석PT 다이어트팩토리짐</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>spotlight_training@naver.com</t>
+          <t>strom9679@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1423-1387</t>
+          <t>0507-1371-7277</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 34 4층 401호, 402호</t>
+          <t>경기도 고양시 일산동구 호수로 358-39 동문굿모닝타워1 B1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://일산다이어트팩토리.com/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4089,7 +4101,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4099,12 +4111,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmf991t</t>
+          <t>https://talk.naver.com/ct/w4cxc1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4113,13 +4125,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>325</v>
       </c>
       <c r="R38" t="n">
-        <v>90</v>
+        <v>507</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4128,12 +4140,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1161024185</t>
+          <t>31119951</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161024185</t>
+          <t>https://m.place.naver.com/place/31119951</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4145,25 +4157,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 24시 중산점</t>
+          <t>온유핏PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1986fitness3@naver.com</t>
+          <t>onu_fit@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1379-8706</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 244 6층</t>
+          <t>경기도 고양시 일산서구 중앙로 1449 7층 704호 온유핏PT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4193,7 +4209,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40uu9</t>
+          <t>https://talk.naver.com/ct/w5xx0n</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4207,13 +4223,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1306</v>
+        <v>63</v>
       </c>
       <c r="Q39" t="n">
-        <v>1295</v>
+        <v>170</v>
       </c>
       <c r="R39" t="n">
-        <v>2601</v>
+        <v>233</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4222,12 +4238,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1052772360</t>
+          <t>1625853344</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1052772360</t>
+          <t>https://m.place.naver.com/place/1625853344</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4239,29 +4255,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 탄현</t>
+          <t>프라임핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>goodhabit_th@naver.com</t>
+          <t>primefit_fitness@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1353-2087</t>
+          <t>031-962-2306</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 75 4층</t>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4286,14 +4302,10 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4a52b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4305,13 +4317,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>144</v>
+        <v>1127</v>
       </c>
       <c r="Q40" t="n">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="R40" t="n">
-        <v>465</v>
+        <v>1416</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4320,12 +4332,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1170704150</t>
+          <t>1328418362</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170704150</t>
+          <t>https://m.place.naver.com/place/1328418362</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4342,24 +4354,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>헌드레드짐 파주운정점</t>
+          <t>어나더짐 풍동본점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hundredgym@naver.com</t>
+          <t>anothergym@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1327-5413</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 파주시 동서대로 640-4 한울빌딩 2층 헌드레드짐</t>
+          <t>경기도 고양시 일산동구 숲속마을로 50-38 중앙프라자 A동 2층 203,204호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4384,10 +4392,14 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48pv9</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>X</t>
@@ -4399,13 +4411,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>529</v>
+        <v>147</v>
       </c>
       <c r="Q41" t="n">
-        <v>203</v>
+        <v>39</v>
       </c>
       <c r="R41" t="n">
-        <v>732</v>
+        <v>186</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4414,12 +4426,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1101743632</t>
+          <t>1490064832</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101743632</t>
+          <t>https://m.place.naver.com/place/1490064832</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4431,49 +4443,49 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>온유핏PT</t>
+          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>onu_fit@naver.com</t>
+          <t>kann666@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1379-8706</t>
+          <t>0507-1428-1174</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1449 7층 704호 온유핏PT</t>
+          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://fitnesskann.com/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4483,12 +4495,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xx0n</t>
+          <t>https://talk.naver.com/ct/w4skng</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4497,13 +4509,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>63</v>
+        <v>1186</v>
       </c>
       <c r="Q42" t="n">
-        <v>170</v>
+        <v>799</v>
       </c>
       <c r="R42" t="n">
-        <v>233</v>
+        <v>1985</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4512,12 +4524,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1625853344</t>
+          <t>1533278650</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1625853344</t>
+          <t>https://m.place.naver.com/place/1533278650</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4529,44 +4541,44 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>라이프바디짐 마두점</t>
+          <t>리스펙짐 PT 백석점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>yok134134@naver.com</t>
+          <t>respect9696@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1381-5774</t>
+          <t>0507-1431-9696</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로196번길 7-5 B1</t>
+          <t>경기도 고양시 일산동구 일산로 142 2층 262-2호, 262-3호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hxfaYG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4576,13 +4588,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7s4785</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4591,13 +4607,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="Q43" t="n">
-        <v>165</v>
+        <v>287</v>
       </c>
       <c r="R43" t="n">
-        <v>295</v>
+        <v>497</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4606,12 +4622,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1899626531</t>
+          <t>1412423288</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899626531</t>
+          <t>https://m.place.naver.com/place/1412423288</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4623,29 +4639,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>제이짐 PT 재활 덕이점</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jgymptrehab@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1345-7048</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 하이파크3로 84 6층 제이짐</t>
+          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4675,12 +4691,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49fg3</t>
+          <t>https://talk.naver.com/ct/wu9oxes</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4689,13 +4705,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="Q44" t="n">
-        <v>684</v>
+        <v>443</v>
       </c>
       <c r="R44" t="n">
-        <v>862</v>
+        <v>686</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4704,12 +4720,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1192308600</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192308600</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4748,7 +4764,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motius_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4758,20 +4774,24 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w6poli2</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -4820,24 +4840,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>슈퍼맨짐PT 대화역점</t>
+          <t>더블엠여성전용운동센터</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dnflwlqrlacl@naver.com</t>
+          <t>ptmickey@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1419-8261</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1565 6층 601호 슈퍼맨짐 대화역점</t>
+          <t>경기도 고양시 일산서구 경의로 665 한뫼프라자 4층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4862,14 +4878,10 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcbcbh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>X</t>
@@ -4877,17 +4889,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="Q46" t="n">
-        <v>373</v>
+        <v>7</v>
       </c>
       <c r="R46" t="n">
-        <v>562</v>
+        <v>63</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4896,12 +4908,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1457573074</t>
+          <t>37616187</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1457573074</t>
+          <t>https://m.place.naver.com/place/37616187</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4918,24 +4930,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>베러모션PT스튜디오 장항점</t>
+          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bmotion01@naver.com</t>
+          <t>gymone10@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1451-0635</t>
+          <t>0507-1328-9681</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1227 동양메이저타워 2층 218호</t>
+          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4965,7 +4977,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7gg1x9</t>
+          <t>https://talk.naver.com/ct/wfhd51g</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4975,17 +4987,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="Q47" t="n">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="R47" t="n">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4994,12 +5006,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1244357356</t>
+          <t>1767374434</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1244357356</t>
+          <t>https://m.place.naver.com/place/1767374434</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5016,24 +5028,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>바디에이원짐 헬스/PT/재활</t>
+          <t>1986피트니스 헬스PT 24시 중산점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>art729@naver.com</t>
+          <t>1986fitness3@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1406-1457</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
+          <t>경기도 고양시 일산동구 중산로 244 6층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5063,7 +5071,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x0ez</t>
+          <t>https://talk.naver.com/ct/w40uu9</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5073,17 +5081,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>543</v>
+        <v>1306</v>
       </c>
       <c r="Q48" t="n">
-        <v>335</v>
+        <v>1297</v>
       </c>
       <c r="R48" t="n">
-        <v>878</v>
+        <v>2603</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5092,12 +5100,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1241623010</t>
+          <t>1052772360</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1241623010</t>
+          <t>https://m.place.naver.com/place/1052772360</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5109,29 +5117,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>트리플에스짐 후곡PT</t>
+          <t>바디에이원짐 헬스/PT/재활</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aplus400@naver.com</t>
+          <t>art729@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1488-9679</t>
+          <t>0507-1406-1457</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 576 대성프라자 2층 207,208호</t>
+          <t>경기도 고양시 일산동구 숲속마을로 18 B1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5161,7 +5169,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wozbktk</t>
+          <t>https://talk.naver.com/ct/w5x0ez</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5171,17 +5179,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>382</v>
+        <v>544</v>
       </c>
       <c r="Q49" t="n">
-        <v>882</v>
+        <v>335</v>
       </c>
       <c r="R49" t="n">
-        <v>1264</v>
+        <v>879</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5190,12 +5198,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1107939487</t>
+          <t>1241623010</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107939487</t>
+          <t>https://m.place.naver.com/place/1241623010</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5207,44 +5215,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>베르만짐 헬스&amp;PT 식사점</t>
+          <t>트리플에스짐 후곡PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>qpfmaks02@naver.com</t>
+          <t>aplus400@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1349-2708</t>
+          <t>0507-1488-9679</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+          <t>경기도 고양시 일산서구 일산로 576 대성프라자 2층 207,208호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhhtNn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5254,13 +5262,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wozbktk</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5269,13 +5281,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="Q50" t="n">
-        <v>670</v>
+        <v>882</v>
       </c>
       <c r="R50" t="n">
-        <v>993</v>
+        <v>1264</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5284,12 +5296,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1722963960</t>
+          <t>1107939487</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722963960</t>
+          <t>https://m.place.naver.com/place/1107939487</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5301,29 +5313,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
+          <t>투게더휘트니스 일산점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>actgym_02@naver.com</t>
+          <t>togetherfitness@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1445-5805</t>
+          <t>0507-1461-1485</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 원일로 69 6층 601호</t>
+          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5353,7 +5365,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wu9oxes</t>
+          <t>https://talk.naver.com/ct/w5zhkh</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5367,13 +5379,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>244</v>
+        <v>1357</v>
       </c>
       <c r="Q51" t="n">
-        <v>442</v>
+        <v>350</v>
       </c>
       <c r="R51" t="n">
-        <v>686</v>
+        <v>1707</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5382,12 +5394,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1033726767</t>
+          <t>1161506645</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033726767</t>
+          <t>https://m.place.naver.com/place/1161506645</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5404,29 +5416,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>developfitness@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1374-2418</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/developfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5436,20 +5448,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5461,13 +5477,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>708</v>
+        <v>1224</v>
       </c>
       <c r="Q52" t="n">
-        <v>1006</v>
+        <v>1611</v>
       </c>
       <c r="R52" t="n">
-        <v>1714</v>
+        <v>2835</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5476,12 +5492,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1332252606</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332252606</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5498,24 +5514,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>일산 에이플러스짐 헬스&amp;PT 마두백마학원가점</t>
+          <t>여성전용 오늘도맑음 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>aplusgym500@naver.com</t>
+          <t>xnlsl@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1449-9334</t>
+          <t>0507-1460-1801</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 229 B1 에이플러스짐 백마학원가점</t>
+          <t>경기도 고양시 일산동구 장백로 184 605호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5545,12 +5561,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl4apt8</t>
+          <t>https://talk.naver.com/ct/w4fd01</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5559,13 +5575,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>488</v>
+        <v>114</v>
       </c>
       <c r="Q53" t="n">
-        <v>680</v>
+        <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>1168</v>
+        <v>123</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5574,12 +5590,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1400678654</t>
+          <t>1282698086</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1400678654</t>
+          <t>https://m.place.naver.com/place/1282698086</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5596,24 +5612,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>재우스짐</t>
+          <t>제이짐 PT 재활 덕이점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>n52003@naver.com</t>
+          <t>jgymptrehab@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1309-1755</t>
+          <t>0507-1345-7048</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 대산로 117</t>
+          <t>경기도 고양시 일산서구 하이파크3로 84 6층 제이짐</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5643,12 +5659,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45pjp</t>
+          <t>https://talk.naver.com/ct/w49fg3</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5657,13 +5673,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>684</v>
       </c>
       <c r="R54" t="n">
-        <v>98</v>
+        <v>862</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5672,12 +5688,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1118529364</t>
+          <t>1192308600</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118529364</t>
+          <t>https://m.place.naver.com/place/1192308600</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5694,24 +5710,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>투게더휘트니스 일산점</t>
+          <t>좋은습관 PT STUDIO 탄현</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>togetherfitness@naver.com</t>
+          <t>goodhabit_th@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1461-1485</t>
+          <t>0507-1353-2087</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
+          <t>경기도 고양시 일산서구 일현로 75 4층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5741,7 +5757,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zhkh</t>
+          <t>https://talk.naver.com/ct/w4a52b</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5755,13 +5771,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1356</v>
+        <v>144</v>
       </c>
       <c r="Q55" t="n">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="R55" t="n">
-        <v>1702</v>
+        <v>465</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5770,12 +5786,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1161506645</t>
+          <t>1170704150</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
+          <t>https://m.place.naver.com/place/1170704150</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5787,29 +5803,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>바틀제로핏</t>
+          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bottlezerofit@naver.com</t>
+          <t>berman_gym@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>031-962-0096</t>
+          <t>0507-1483-3436</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 견달산로 268 2층(씨카우마트2층)</t>
+          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5839,7 +5855,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hco7</t>
+          <t>https://talk.naver.com/ct/wvt0jtv</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5853,13 +5869,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>1559</v>
       </c>
       <c r="R56" t="n">
-        <v>34</v>
+        <v>2250</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5868,12 +5884,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1227017459</t>
+          <t>1924109138</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1227017459</t>
+          <t>https://m.place.naver.com/place/1924109138</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5885,29 +5901,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>여성전용 포레스트짐 PT&amp;헬스 장항점</t>
+          <t>리스펙짐 PT 마두점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>lifetime1231@naver.com</t>
+          <t>respect1333@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1355-9897</t>
+          <t>0507-1335-1380</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 17 라고프라자 305호 여성전용 포레스트짐PT</t>
+          <t>경기도 고양시 일산동구 강석로 123 뉴삼창 빌딩 9층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5937,7 +5953,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wsf5729</t>
+          <t>https://talk.naver.com/ct/w4lzon</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5951,13 +5967,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>491</v>
+        <v>1376</v>
       </c>
       <c r="Q57" t="n">
-        <v>1140</v>
+        <v>1393</v>
       </c>
       <c r="R57" t="n">
-        <v>1631</v>
+        <v>2769</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5966,12 +5982,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1618140538</t>
+          <t>1420492815</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1618140538</t>
+          <t>https://m.place.naver.com/place/1420492815</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5983,29 +5999,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>씨더블유PT</t>
+          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>tlscnddn2@naver.com</t>
+          <t>maxoutfitness_1@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-0178-6183</t>
+          <t>0507-1378-6366</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로 662 2층 217호</t>
+          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6035,7 +6051,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f6ar</t>
+          <t>https://talk.naver.com/ct/w42bdj</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6049,13 +6065,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>104</v>
+        <v>1276</v>
       </c>
       <c r="Q58" t="n">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="R58" t="n">
-        <v>226</v>
+        <v>1479</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6064,12 +6080,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1675929212</t>
+          <t>1674766909</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675929212</t>
+          <t>https://m.place.naver.com/place/1674766909</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6081,25 +6097,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>에이플러스짐휘트니스센터 백마학원가점</t>
+          <t>씨더블유PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>aplusgym500@naver.com</t>
+          <t>tlscnddn2@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-0178-6183</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
+          <t>경기도 고양시 일산동구 호수로 662 2층 217호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6129,7 +6149,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl4apt8</t>
+          <t>https://talk.naver.com/ct/w4f6ar</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6143,13 +6163,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="Q59" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="R59" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6158,12 +6178,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2067321363</t>
+          <t>1675929212</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067321363</t>
+          <t>https://m.place.naver.com/place/1675929212</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6180,44 +6200,44 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>레디바디 탄현점 헬스PT</t>
+          <t>여성전용 포레스트짐 헬스&amp;피티 주엽점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>readybody2@naver.com</t>
+          <t>olof7l6h@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1359-9680</t>
+          <t>0507-1431-9036</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
+          <t>경기도 고양시 일산서구 주엽로 150 자유프라자 9층 906호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://link.inpock.co.kr/forestgym_2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6227,7 +6247,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w461vb</t>
+          <t>https://talk.naver.com/ct/w5yfab</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6241,13 +6261,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>679</v>
+        <v>857</v>
       </c>
       <c r="Q60" t="n">
-        <v>1056</v>
+        <v>539</v>
       </c>
       <c r="R60" t="n">
-        <v>1735</v>
+        <v>1396</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6256,12 +6276,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>776760797</t>
+          <t>1320621577</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/776760797</t>
+          <t>https://m.place.naver.com/place/1320621577</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6278,24 +6298,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>여성전용PT 핏바디짐</t>
+          <t>원잇핏 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>fitbodygym_@naver.com</t>
+          <t>oneitfit@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1331-7858</t>
+          <t>0507-1400-8861</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 대산로 116 305호</t>
+          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6325,7 +6345,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4vtrh</t>
+          <t>https://talk.naver.com/ct/w46eey</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6339,13 +6359,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>29</v>
+        <v>229</v>
       </c>
       <c r="Q61" t="n">
-        <v>64</v>
+        <v>596</v>
       </c>
       <c r="R61" t="n">
-        <v>93</v>
+        <v>825</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6354,12 +6374,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1315910427</t>
+          <t>13223584</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315910427</t>
+          <t>https://m.place.naver.com/place/13223584</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6371,25 +6391,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>더블엠여성전용운동센터</t>
+          <t>테디케이짐 헬스 PT 풍동점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ptmickey@naver.com</t>
+          <t>teddykgym@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1483-6336</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 경의로 665 한뫼프라자 4층</t>
+          <t>경기도 고양시 일산동구 숲속마을로 26 7층 701호(7층전체)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6414,10 +6438,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjaytn7</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
           <t>X</t>
@@ -6425,17 +6453,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>56</v>
+        <v>539</v>
       </c>
       <c r="Q62" t="n">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="R62" t="n">
-        <v>63</v>
+        <v>796</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6444,12 +6472,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>37616187</t>
+          <t>1011101134</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37616187</t>
+          <t>https://m.place.naver.com/place/1011101134</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6461,29 +6489,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>맥스아웃휘트니스 동구청점 헬스 PT 골프</t>
+          <t>제니필라테스 백석점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>maxoutfitness_1@naver.com</t>
+          <t>jenny_3433@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1378-6366</t>
+          <t>0507-1459-3489</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 47 6층 605~608호</t>
+          <t>경기도 고양시 일산동구 장백로 56 크리스탈빌딩 6층 604호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6513,7 +6541,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42bdj</t>
+          <t>https://talk.naver.com/ct/wqg39jj</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6527,13 +6555,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1274</v>
+        <v>148</v>
       </c>
       <c r="Q63" t="n">
-        <v>203</v>
+        <v>343</v>
       </c>
       <c r="R63" t="n">
-        <v>1477</v>
+        <v>491</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6542,12 +6570,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1674766909</t>
+          <t>592860746</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674766909</t>
+          <t>https://m.place.naver.com/place/592860746</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6564,29 +6592,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>고포잇짐 헬스&amp;PT 장항점</t>
+          <t>슈퍼맨짐PT 대화역점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>go4itgym1@naver.com</t>
+          <t>dnflwlqrlacl@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1315-5550</t>
+          <t>0507-1419-8261</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
+          <t>경기도 고양시 일산서구 중앙로 1565 6층 601호 슈퍼맨짐 대화역점</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/go4itgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6596,20 +6624,24 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcbcbh</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>X</t>
@@ -6621,13 +6653,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="Q64" t="n">
-        <v>712</v>
+        <v>374</v>
       </c>
       <c r="R64" t="n">
-        <v>876</v>
+        <v>563</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6636,12 +6668,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1738952122</t>
+          <t>1457573074</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738952122</t>
+          <t>https://m.place.naver.com/place/1457573074</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6653,29 +6685,29 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
+          <t>헬로우짐 헬스&amp;PT 백석점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>berman_gym@naver.com</t>
+          <t>hellogym001@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1483-3436</t>
+          <t>0507-1383-8244</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
+          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6705,12 +6737,12 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wvt0jtv</t>
+          <t>https://talk.naver.com/ct/w4cr18</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6719,13 +6751,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>689</v>
+        <v>100</v>
       </c>
       <c r="Q65" t="n">
-        <v>1558</v>
+        <v>220</v>
       </c>
       <c r="R65" t="n">
-        <v>2247</v>
+        <v>320</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6734,12 +6766,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1924109138</t>
+          <t>1528105437</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924109138</t>
+          <t>https://m.place.naver.com/place/1528105437</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6756,24 +6788,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>메피 운동의학 GYM</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mephy_9801@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>031-963-4236</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 14-26 류정빌딩 3층</t>
+          <t>경기도 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6798,10 +6830,14 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>X</t>
@@ -6809,17 +6845,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>15</v>
+        <v>1254</v>
       </c>
       <c r="Q66" t="n">
-        <v>39</v>
+        <v>1091</v>
       </c>
       <c r="R66" t="n">
-        <v>54</v>
+        <v>2345</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6828,12 +6864,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>21127933</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21127933</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6845,29 +6881,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>에이플러스짐 PT 중산점</t>
+          <t>디노짐 헬스PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>aplusgym600@naver.com</t>
+          <t>dinogym2023@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>031-977-5755</t>
+          <t>0507-1341-5664</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
+          <t>경기도 고양시 일산서구 일현로 38 세진프라자 3층 디노짐</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6897,7 +6933,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w2t1k29</t>
+          <t>https://talk.naver.com/ct/w4fu7p</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6911,13 +6947,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="Q67" t="n">
-        <v>740</v>
+        <v>252</v>
       </c>
       <c r="R67" t="n">
-        <v>1229</v>
+        <v>700</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6926,12 +6962,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1426431657</t>
+          <t>1693675710</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426431657</t>
+          <t>https://m.place.naver.com/place/1693675710</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6948,24 +6984,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>짐원휘트니스 주엽10호점 헬스PT골프</t>
+          <t>탑 메디컬 트레이닝&amp;pt</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>gymone10@naver.com</t>
+          <t>woosc9090@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1328-9681</t>
+          <t>0507-1303-3474</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1391 레이크타운쇼핑 상가동 3층</t>
+          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6995,7 +7031,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfhd51g</t>
+          <t>https://talk.naver.com/ct/w4mk8a</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7005,17 +7041,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="Q68" t="n">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="R68" t="n">
-        <v>297</v>
+        <v>112</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -7024,12 +7060,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1767374434</t>
+          <t>1747685925</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767374434</t>
+          <t>https://m.place.naver.com/place/1747685925</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7046,24 +7082,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>에이치핏PT&amp;헬스</t>
+          <t>여성전용PT 핏바디짐</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>dngus8888@naver.com</t>
+          <t>fitbodygym_@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1426-3482</t>
+          <t>0507-1331-7858</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1547 3층 307호</t>
+          <t>경기도 고양시 일산서구 대산로 116 305호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7093,12 +7129,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zrcp</t>
+          <t>https://talk.naver.com/ct/w4vtrh</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7107,13 +7143,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="Q69" t="n">
-        <v>337</v>
+        <v>64</v>
       </c>
       <c r="R69" t="n">
-        <v>409</v>
+        <v>94</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7122,12 +7158,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1639222494</t>
+          <t>1315910427</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639222494</t>
+          <t>https://m.place.naver.com/place/1315910427</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7144,24 +7180,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>헬로우짐 헬스&amp;PT 백석점</t>
+          <t>고포잇짐 헬스&amp;PT 장항점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hellogym001@naver.com</t>
+          <t>go4itgym1@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1383-8244</t>
+          <t>0507-1315-5550</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1048 르메이에르프라자 3층 헬로우짐</t>
+          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7191,7 +7227,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cr18</t>
+          <t>https://talk.naver.com/ct/w4i1nr</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7205,13 +7241,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="Q70" t="n">
-        <v>220</v>
+        <v>711</v>
       </c>
       <c r="R70" t="n">
-        <v>320</v>
+        <v>875</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7220,12 +7256,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1528105437</t>
+          <t>1738952122</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1528105437</t>
+          <t>https://m.place.naver.com/place/1738952122</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7242,24 +7278,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>더핏퍼스널트레이닝</t>
+          <t>여성전용헬스갸르핏</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sky_se@naver.com</t>
+          <t>garfitness@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1411-0772</t>
+          <t>0507-1346-1822</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
+          <t>경기도 고양시 일산동구 정발산로 15 3층 311호(장항동, 드림월드빌딩)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7289,7 +7325,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4izrx</t>
+          <t>https://talk.naver.com/ct/w4b2kq</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7303,13 +7339,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="Q71" t="n">
-        <v>1130</v>
+        <v>153</v>
       </c>
       <c r="R71" t="n">
-        <v>1311</v>
+        <v>206</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7318,12 +7354,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1707178271</t>
+          <t>1015924009</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1707178271</t>
+          <t>https://m.place.naver.com/place/1015924009</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7340,29 +7376,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>더바디핏PT&amp;헬스</t>
+          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>seung5105@naver.com</t>
+          <t>resort_13@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1398-9610</t>
+          <t>0507-1434-4080</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 대산로212번길 24-27 지하1층</t>
+          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/resort_13</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7372,24 +7408,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yi3h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>X</t>
@@ -7401,13 +7433,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>27</v>
+        <v>562</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>907</v>
       </c>
       <c r="R72" t="n">
-        <v>39</v>
+        <v>1469</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7416,12 +7448,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1689017315</t>
+          <t>1379874016</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689017315</t>
+          <t>https://m.place.naver.com/place/1379874016</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7433,29 +7465,29 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>차차필라테스앤피티 정발산점</t>
+          <t>더핏퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>chachapila@naver.com</t>
+          <t>sky_se@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1447-9945</t>
+          <t>0507-1411-0772</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 34 4층 406호</t>
+          <t>경기도 고양시 일산동구 중앙로 1194 금강프라자 5층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7485,7 +7517,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41ik9</t>
+          <t>https://talk.naver.com/ct/w4izrx</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7499,13 +7531,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="Q73" t="n">
-        <v>367</v>
+        <v>1131</v>
       </c>
       <c r="R73" t="n">
-        <v>513</v>
+        <v>1312</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7514,12 +7546,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1185573190</t>
+          <t>1707178271</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185573190</t>
+          <t>https://m.place.naver.com/place/1707178271</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7531,17 +7563,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>어나더짐 풍동본점</t>
+          <t>에이플러스짐휘트니스센터 백마학원가점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>anothergym@naver.com</t>
+          <t>aplusgym500@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -7549,7 +7581,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 숲속마을로 50-38 중앙프라자 A동 2층 203,204호</t>
+          <t>경기도 고양시 일산동구 일산로 229 지하1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7579,7 +7611,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48pv9</t>
+          <t>https://talk.naver.com/ct/wl4apt8</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -7593,13 +7625,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="Q74" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="R74" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7608,12 +7640,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1490064832</t>
+          <t>2067321363</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490064832</t>
+          <t>https://m.place.naver.com/place/2067321363</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7630,24 +7662,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>원잇핏 PT&amp;헬스</t>
+          <t>로드짐 야당점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>oneitfit@naver.com</t>
+          <t>roadgym86@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1400-8861</t>
+          <t>0507-1458-6779</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 강성로 101 제일프라자 5층</t>
+          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7677,12 +7709,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46eey</t>
+          <t>https://talk.naver.com/ct/w44xex</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7691,13 +7723,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="Q75" t="n">
-        <v>595</v>
+        <v>116</v>
       </c>
       <c r="R75" t="n">
-        <v>824</v>
+        <v>197</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7706,12 +7738,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>13223584</t>
+          <t>1959563259</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13223584</t>
+          <t>https://m.place.naver.com/place/1959563259</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7728,24 +7760,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>여성전용 오늘도맑음 PT&amp;헬스</t>
+          <t>바로그짐 풍동점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>xnlsl@naver.com</t>
+          <t>barofitness@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1460-1801</t>
+          <t>0507-1428-3551</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 장백로 184 605호</t>
+          <t>경기도 고양시 일산동구 애니골길 38 바로그짐</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7775,7 +7807,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fd01</t>
+          <t>https://talk.naver.com/ct/w5uwxf</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7789,13 +7821,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="Q76" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="R76" t="n">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7804,12 +7836,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1282698086</t>
+          <t>1452871805</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1282698086</t>
+          <t>https://m.place.naver.com/place/1452871805</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_health/일산_PT.xlsx
+++ b/naver-place-crawler/results_health/일산_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 일산점</t>
+          <t>에이플러스짐 PT 중산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rewind9089@naver.com</t>
+          <t>aplusgym600@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1414-2729</t>
+          <t>031-977-5755</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 60 5층 리와인드휘트니스</t>
+          <t>경기도 고양시 일산동구 중산로 63 현대프라자 202호 에이플러스짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://linktr.ee/junistar3579</t>
+          <t>https://blog.naver.com/aplusgym600/222983159417</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>340</v>
+        <v>489</v>
       </c>
       <c r="Q2" t="n">
-        <v>204</v>
+        <v>740</v>
       </c>
       <c r="R2" t="n">
-        <v>544</v>
+        <v>1229</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1294694330</t>
+          <t>1426431657</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294694330</t>
+          <t>https://m.place.naver.com/place/1426431657</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리와인드 휘트니스 중산점</t>
+          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rewind_8990@naver.com</t>
+          <t>healthboy67@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1300-9146</t>
+          <t>0507-1373-7656</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로 762 406~412호</t>
+          <t>경기 고양시 일산서구 중앙로 1496 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rewind_fitness2</t>
+          <t>https://linktr.ee/healthboygym67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +695,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dgq8</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>167</v>
+        <v>617</v>
       </c>
       <c r="Q3" t="n">
-        <v>138</v>
+        <v>791</v>
       </c>
       <c r="R3" t="n">
-        <v>305</v>
+        <v>1408</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1726802714</t>
+          <t>1251452457</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726802714</t>
+          <t>https://m.place.naver.com/place/1251452457</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1217,34 +1221,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>탑 메디컬 트레이닝&amp;pt</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>woosc9090@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1303-3474</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1305-56 라페스타 D동 2층 215호</t>
+          <t>경기도 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woosc9090</t>
+          <t>https://blog.naver.com/readybody2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>29</v>
+        <v>679</v>
       </c>
       <c r="Q9" t="n">
-        <v>83</v>
+        <v>1060</v>
       </c>
       <c r="R9" t="n">
-        <v>112</v>
+        <v>1739</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1747685925</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747685925</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이치짐 헬스&amp;PT 야당점</t>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ssj783312@naver.com</t>
+          <t>bodyoffgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-943-0116</t>
+          <t>0507-1381-8260</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1070 호수프라자 6층 에이치짐</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hgym24/</t>
+          <t>https://blog.naver.com/bodyoffgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>367</v>
+        <v>133</v>
       </c>
       <c r="Q10" t="n">
-        <v>421</v>
+        <v>510</v>
       </c>
       <c r="R10" t="n">
-        <v>788</v>
+        <v>643</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>548127191</t>
+          <t>32507674</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/548127191</t>
+          <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1409,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
+          <t>프라임핏 헬스&amp;PT 식사점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyoffgym@naver.com</t>
+          <t>primefit_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1381-8260</t>
+          <t>031-962-2306</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
+          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyoffgym</t>
+          <t>https://www.instagram.com/prime_fit1/?igshid=MWpldjY4Y3h2dDF4ag%3D%3D</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>133</v>
+        <v>1126</v>
       </c>
       <c r="Q11" t="n">
-        <v>510</v>
+        <v>289</v>
       </c>
       <c r="R11" t="n">
-        <v>643</v>
+        <v>1415</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32507674</t>
+          <t>1328418362</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32507674</t>
+          <t>https://m.place.naver.com/place/1328418362</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,29 +1508,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>프라임핏 헬스&amp;PT 식사점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>primefit_fitness@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>031-962-2306</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티1로 6-39 더파인테라스 3층 프라임핏</t>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/prime_fit1/?igshid=MWpldjY4Y3h2dDF4ag%3D%3D</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1541,7 +1545,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1126</v>
+        <v>304</v>
       </c>
       <c r="Q12" t="n">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="R12" t="n">
-        <v>1415</v>
+        <v>574</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,109 +1580,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1328418362</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328418362</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lounge_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1360-7495</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>304</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>270</v>
-      </c>
-      <c r="R13" t="n">
-        <v>574</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1798562504</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
